--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -863,7 +863,7 @@
         <v>1.27</v>
       </c>
       <c r="H2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
         <v>16</v>
@@ -890,7 +890,7 @@
         <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 00:24:32</t>
+          <t>2026-07-11 02:42:49</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 00:24:32</t>
+          <t>2026-07-11 02:42:49</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
@@ -1413,10 +1413,10 @@
         <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 00:24:32</t>
+          <t>2026-07-11 02:42:49</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="I5" t="n">
         <v>2.92</v>
@@ -1643,13 +1643,13 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q5" t="n">
         <v>2.48</v>
@@ -1661,22 +1661,22 @@
         <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
         <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
         <v>21</v>
@@ -1697,10 +1697,10 @@
         <v>48</v>
       </c>
       <c r="AF5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
         <v>26</v>
@@ -1709,16 +1709,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
         <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
         <v>65</v>
@@ -1733,10 +1733,10 @@
         <v>7.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1751,22 +1751,22 @@
         <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
       </c>
       <c r="BB5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.9</v>
       </c>
       <c r="BD5" t="n">
         <v>5.1</v>
@@ -1778,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.86</v>
@@ -1790,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,22 +1802,22 @@
         <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU5" t="n">
         <v>4.2</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 00:24:32</t>
+          <t>2026-07-11 02:42:49</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 00:24:32</t>
+          <t>2026-07-11 02:42:49</t>
         </is>
       </c>
     </row>
@@ -2142,10 +2142,10 @@
         <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
@@ -2277,7 +2277,7 @@
         <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.6</v>
+        <v>42</v>
       </c>
       <c r="BE7" t="n">
         <v>6</v>
@@ -2289,68 +2289,68 @@
         <v>6</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 00:24:32</t>
+          <t>2026-07-11 02:42:49</t>
         </is>
       </c>
     </row>
@@ -2390,10 +2390,10 @@
         <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
@@ -2405,16 +2405,16 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
         <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>1.21</v>
@@ -2429,7 +2429,7 @@
         <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
         <v>1.71</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 00:24:32</t>
+          <t>2026-07-11 02:42:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
         <v>1.27</v>
@@ -872,7 +872,7 @@
         <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
         <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>1.44</v>
@@ -1398,7 +1398,7 @@
         <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -1416,7 +1416,7 @@
         <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1431,7 +1431,7 @@
         <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.199999999999999</v>
@@ -1443,7 +1443,7 @@
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1482,10 +1482,10 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1503,7 +1503,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
         <v>42</v>
@@ -1515,10 +1515,10 @@
         <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
         <v>13</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I5" t="n">
         <v>2.92</v>
@@ -1643,13 +1643,13 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
         <v>2.48</v>
@@ -1661,22 +1661,22 @@
         <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
         <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
         <v>21</v>
@@ -1697,10 +1697,10 @@
         <v>48</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>26</v>
@@ -1709,16 +1709,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK5" t="n">
         <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="n">
         <v>65</v>
@@ -1733,16 +1733,16 @@
         <v>7.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
         <v>11</v>
@@ -1751,22 +1751,22 @@
         <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="BD5" t="n">
         <v>5.1</v>
@@ -1778,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="BH5" t="n">
         <v>2.86</v>
@@ -1790,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,22 +1802,22 @@
         <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU5" t="n">
         <v>4.2</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>1.96</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
         <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2175,34 +2175,34 @@
         <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="X7" t="n">
         <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
         <v>50</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB7" t="n">
         <v>7.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -2217,7 +2217,7 @@
         <v>120</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
         <v>32</v>
@@ -2226,13 +2226,13 @@
         <v>75</v>
       </c>
       <c r="AM7" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP7" t="n">
         <v>7.4</v>
@@ -2244,7 +2244,7 @@
         <v>25</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>6</v>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
         <v>9.4</v>
@@ -2268,7 +2268,7 @@
         <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
         <v>19.5</v>
@@ -2280,13 +2280,13 @@
         <v>42</v>
       </c>
       <c r="BE7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
         <v>17.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="n">
         <v>2.98</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
         <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
         <v>1.51</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="n">
         <v>1.27</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>4.4</v>
@@ -1404,7 +1404,7 @@
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
         <v>1.9</v>
@@ -1416,7 +1416,7 @@
         <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1634,49 +1634,49 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
         <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
         <v>21</v>
@@ -1685,79 +1685,79 @@
         <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
         <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
         <v>24</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN5" t="n">
         <v>70</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>65</v>
       </c>
       <c r="AO5" t="n">
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR5" t="n">
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
         <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1769,10 +1769,10 @@
         <v>34</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
         <v>5</v>
@@ -1781,22 +1781,22 @@
         <v>34</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2381,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
         <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>2.44</v>
@@ -2417,10 +2417,10 @@
         <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
         <v>1.97</v>
@@ -2429,7 +2429,7 @@
         <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
         <v>1.71</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>Ningbo Professional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Foshan Nanshi FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
         <v>1.27</v>
       </c>
-      <c r="H2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="K2" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 07:19:53</t>
+          <t>2026-07-11 09:37:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 07:19:53</t>
+          <t>2026-07-11 09:37:40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
         <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 07:19:53</t>
+          <t>2026-07-11 09:37:40</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.94</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.94</v>
       </c>
       <c r="X5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>11</v>
       </c>
-      <c r="Y5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>9.6</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 07:19:53</t>
+          <t>2026-07-11 09:37:40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,168 +1859,168 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
         <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
         <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO6" t="n">
         <v>55</v>
       </c>
-      <c r="AL6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>60</v>
-      </c>
       <c r="AP6" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AS6" t="n">
         <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="BD6" t="n">
         <v>5</v>
@@ -2029,81 +2029,81 @@
         <v>5.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>34</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.06</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.14</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.14</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 07:19:53</t>
+          <t>2026-07-11 09:37:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,498 +2113,752 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.43</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.93</v>
-      </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
         <v>75</v>
       </c>
       <c r="AM7" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AR7" t="n">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AT7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN7" t="n">
         <v>6</v>
       </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BO7" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.4</v>
+        <v>2.06</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.4</v>
+        <v>2.14</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BU7" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>9</v>
+        <v>2.06</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.4</v>
+        <v>2.14</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.4</v>
+        <v>2.14</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 07:19:53</t>
+          <t>2026-07-11 09:37:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-11 09:37:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Figueirense</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>950</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="G9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
         <v>1.01</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS9" t="n">
         <v>2.16</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE8" t="n">
+      <c r="BT9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU9" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BR8" t="n">
+      <c r="BV9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>44</v>
       </c>
-      <c r="BS8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW8" t="n">
+      <c r="CA9" t="n">
         <v>2.16</v>
       </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>46</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-11 07:19:53</t>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-11 09:37:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 09:37:40</t>
+          <t>2026-07-11 11:55:11</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="H3" t="n">
         <v>12</v>
@@ -1123,10 +1123,10 @@
         <v>14.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="K3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
         <v>1.52</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 09:37:40</t>
+          <t>2026-07-11 11:55:11</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 09:37:40</t>
+          <t>2026-07-11 11:55:11</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -1631,7 +1631,7 @@
         <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
         <v>3.7</v>
@@ -1646,7 +1646,7 @@
         <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
         <v>1.83</v>
@@ -1670,7 +1670,7 @@
         <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1700,7 +1700,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
@@ -1712,7 +1712,7 @@
         <v>32</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>50</v>
@@ -1724,10 +1724,10 @@
         <v>21</v>
       </c>
       <c r="AO5" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>9.6</v>
@@ -1736,7 +1736,7 @@
         <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
         <v>7.4</v>
@@ -1769,16 +1769,16 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 09:37:40</t>
+          <t>2026-07-11 11:55:11</t>
         </is>
       </c>
     </row>
@@ -1894,13 +1894,13 @@
         <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
         <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
         <v>1.53</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 09:37:40</t>
+          <t>2026-07-11 11:55:11</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 09:37:40</t>
+          <t>2026-07-11 11:55:11</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.96</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
         <v>4.7</v>
@@ -2432,7 +2432,7 @@
         <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 09:37:40</t>
+          <t>2026-07-11 11:55:11</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-11 09:37:40</t>
+          <t>2026-07-11 11:55:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 11:55:11</t>
+          <t>2026-07-11 14:12:02</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H3" t="n">
         <v>12</v>
@@ -1129,16 +1129,16 @@
         <v>7.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
         <v>2.68</v>
@@ -1147,194 +1147,194 @@
         <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 11:55:11</t>
+          <t>2026-07-11 14:12:02</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 11:55:11</t>
+          <t>2026-07-11 14:12:02</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 11:55:11</t>
+          <t>2026-07-11 14:12:02</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
         <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
         <v>2.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 11:55:11</t>
+          <t>2026-07-11 14:12:02</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>2.82</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -2160,19 +2160,19 @@
         <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
         <v>1.46</v>
@@ -2235,37 +2235,37 @@
         <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
         <v>4.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.95</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
         <v>4.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
         <v>5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 11:55:11</t>
+          <t>2026-07-11 14:12:02</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
@@ -2498,7 +2498,7 @@
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT8" t="n">
         <v>6</v>
@@ -2522,7 +2522,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
         <v>19.5</v>
@@ -2534,13 +2534,13 @@
         <v>42</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="n">
         <v>2.98</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 11:55:11</t>
+          <t>2026-07-11 14:12:02</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
         <v>4.2</v>
@@ -2650,7 +2650,7 @@
         <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
         <v>1.44</v>
@@ -2659,28 +2659,28 @@
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
         <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
         <v>1.31</v>
@@ -2755,10 +2755,10 @@
         <v>4.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="AV9" t="n">
         <v>3.95</v>
@@ -2770,7 +2770,7 @@
         <v>3.85</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
         <v>4.2</v>
@@ -2797,7 +2797,7 @@
         <v>4.7</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI9" t="n">
         <v>2.32</v>
@@ -2806,34 +2806,34 @@
         <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.26</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>5.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>42</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.16</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
         <v>4.2</v>
@@ -2842,23 +2842,23 @@
         <v>38</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.2</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>44</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.16</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-11 11:55:11</t>
+          <t>2026-07-11 14:12:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:12:02</t>
+          <t>2026-07-11 16:28:06</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.26</v>
       </c>
       <c r="G3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H3" t="n">
         <v>12</v>
@@ -1135,7 +1135,7 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
@@ -1147,194 +1147,194 @@
         <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN3" t="n">
         <v>4.3</v>
       </c>
-      <c r="X3" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.65</v>
+        <v>36</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.65</v>
+        <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BA3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB3" t="n">
         <v>9</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BF3" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="BJ3" t="n">
         <v>17</v>
       </c>
       <c r="BK3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>22</v>
+        <v>2.1</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="BP3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
         <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>13.5</v>
+        <v>1.97</v>
       </c>
       <c r="BT3" t="n">
         <v>22</v>
       </c>
       <c r="BU3" t="n">
-        <v>10</v>
+        <v>1.92</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>22</v>
+        <v>2.1</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>22</v>
+        <v>2.1</v>
       </c>
       <c r="BZ3" t="n">
         <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 14:12:02</t>
+          <t>2026-07-11 16:28:06</t>
         </is>
       </c>
     </row>
@@ -1383,16 +1383,16 @@
         <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P4" t="n">
         <v>3.5</v>
@@ -1401,194 +1401,194 @@
         <v>1.31</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 14:12:02</t>
+          <t>2026-07-11 16:28:06</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
         <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1769,10 +1769,10 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 14:12:02</t>
+          <t>2026-07-11 16:28:06</t>
         </is>
       </c>
     </row>
@@ -1984,13 +1984,13 @@
         <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
         <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>38</v>
       </c>
       <c r="AT6" t="n">
         <v>7.8</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 14:12:02</t>
+          <t>2026-07-11 16:28:06</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
         <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>10</v>
@@ -2217,7 +2217,7 @@
         <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
         <v>55</v>
@@ -2229,7 +2229,7 @@
         <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO7" t="n">
         <v>60</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 14:12:02</t>
+          <t>2026-07-11 16:28:06</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.96</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
         <v>4.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 14:12:02</t>
+          <t>2026-07-11 16:28:06</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
         <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
         <v>1.82</v>
@@ -2818,7 +2818,7 @@
         <v>5.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP9" t="n">
         <v>21</v>
@@ -2836,7 +2836,7 @@
         <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>38</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-11 14:12:02</t>
+          <t>2026-07-11 16:28:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 16:28:06</t>
+          <t>2026-07-11 18:44:38</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
         <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 16:28:06</t>
+          <t>2026-07-11 18:44:38</t>
         </is>
       </c>
     </row>
@@ -1407,10 +1407,10 @@
         <v>1.79</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="V4" t="n">
         <v>1.29</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 16:28:06</t>
+          <t>2026-07-11 18:44:38</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 16:28:06</t>
+          <t>2026-07-11 18:44:38</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
         <v>2.92</v>
@@ -1906,7 +1906,7 @@
         <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R6" t="n">
         <v>1.19</v>
@@ -1924,13 +1924,13 @@
         <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
@@ -1939,7 +1939,7 @@
         <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
@@ -1951,7 +1951,7 @@
         <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
         <v>17.5</v>
@@ -1969,13 +1969,13 @@
         <v>60</v>
       </c>
       <c r="AL6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM6" t="n">
         <v>210</v>
       </c>
       <c r="AN6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO6" t="n">
         <v>55</v>
@@ -1984,16 +1984,16 @@
         <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
@@ -2002,10 +2002,10 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
@@ -2014,22 +2014,22 @@
         <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
         <v>34</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG6" t="n">
         <v>34</v>
@@ -2044,7 +2044,7 @@
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2086,7 +2086,7 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 16:28:06</t>
+          <t>2026-07-11 18:44:38</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 16:28:06</t>
+          <t>2026-07-11 18:44:38</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 16:28:06</t>
+          <t>2026-07-11 18:44:38</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="I9" t="n">
         <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.45</v>
@@ -2674,7 +2674,7 @@
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
         <v>1.99</v>
@@ -2686,7 +2686,7 @@
         <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="X9" t="n">
         <v>11.5</v>
@@ -2701,7 +2701,7 @@
         <v>90</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
         <v>8.6</v>
@@ -2716,7 +2716,7 @@
         <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>26</v>
@@ -2743,16 +2743,16 @@
         <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
         <v>6.6</v>
@@ -2761,40 +2761,40 @@
         <v>5.5</v>
       </c>
       <c r="AV9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX9" t="n">
         <v>3.95</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.85</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC9" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH9" t="n">
         <v>2.92</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-11 16:28:06</t>
+          <t>2026-07-11 18:44:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -887,7 +887,7 @@
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
         <v>1.48</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -923,7 +923,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
         <v>1000</v>
@@ -947,7 +947,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>1000</v>
@@ -965,49 +965,49 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
         <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
         <v>1.03</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 18:44:38</t>
+          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>1.28</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
         <v>6.8</v>
@@ -1129,43 +1129,43 @@
         <v>7.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
         <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
         <v>4.4</v>
       </c>
       <c r="X3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="n">
         <v>48</v>
@@ -1180,10 +1180,10 @@
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AE3" t="n">
         <v>240</v>
@@ -1192,67 +1192,67 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AK3" t="n">
         <v>14.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
         <v>13.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1261,80 +1261,80 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BJ3" t="n">
         <v>17</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BP3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR3" t="n">
         <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="BT3" t="n">
         <v>22</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BZ3" t="n">
         <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 18:44:38</t>
+          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
         <v>1.89</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,31 +1389,31 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.07</v>
       </c>
-      <c r="P4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.31</v>
-      </c>
       <c r="R4" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.79</v>
+        <v>1.07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
         <v>2.12</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 18:44:38</t>
+          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
@@ -1655,7 +1655,7 @@
         <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
         <v>3.9</v>
@@ -1676,7 +1676,7 @@
         <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
@@ -1685,164 +1685,164 @@
         <v>95</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>60</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
         <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>38</v>
-      </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BF5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>13</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
         <v>15</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>2.92</v>
       </c>
       <c r="BR5" t="n">
         <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>11.5</v>
+        <v>3.25</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW5" t="n">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY5" t="n">
-        <v>13</v>
+        <v>3.35</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA5" t="n">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 18:44:38</t>
+          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>
@@ -1873,28 +1873,28 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.98</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
         <v>2.6</v>
@@ -1906,79 +1906,79 @@
         <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
         <v>1.41</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
         <v>75</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
         <v>6.6</v>
@@ -1990,19 +1990,19 @@
         <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
         <v>14.5</v>
@@ -2011,28 +2011,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
         <v>2.8</v>
@@ -2074,10 +2074,10 @@
         <v>5.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW6" t="n">
         <v>8.199999999999999</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 18:44:38</t>
+          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.82</v>
+        <v>2.18</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>1.44</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 18:44:38</t>
+          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
         <v>4.7</v>
@@ -2399,13 +2399,13 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
         <v>1.46</v>
@@ -2423,46 +2423,46 @@
         <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
         <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB8" t="n">
         <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
@@ -2477,16 +2477,16 @@
         <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP8" t="n">
         <v>7.4</v>
@@ -2495,10 +2495,10 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
         <v>6</v>
@@ -2510,10 +2510,10 @@
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
@@ -2522,7 +2522,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
         <v>19.5</v>
@@ -2531,16 +2531,16 @@
         <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
         <v>2.98</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 18:44:38</t>
+          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="G9" t="n">
         <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
@@ -2671,10 +2671,10 @@
         <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
       <c r="T9" t="n">
         <v>1.99</v>
@@ -2683,7 +2683,7 @@
         <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
         <v>1.71</v>
@@ -2692,25 +2692,25 @@
         <v>11.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="n">
         <v>16.5</v>
@@ -2719,13 +2719,13 @@
         <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK9" t="n">
         <v>38</v>
@@ -2734,13 +2734,13 @@
         <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
         <v>38</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP9" t="n">
         <v>7.2</v>
@@ -2749,10 +2749,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
         <v>6.6</v>
@@ -2761,104 +2761,104 @@
         <v>5.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AX9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB9" t="n">
         <v>3.95</v>
       </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
+      <c r="BC9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5</v>
-      </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>1.43</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>1.43</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.8</v>
+        <v>1.43</v>
       </c>
       <c r="BP9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7</v>
+        <v>1.43</v>
       </c>
       <c r="BR9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.4</v>
+        <v>1.43</v>
       </c>
       <c r="BT9" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>1.43</v>
       </c>
       <c r="BV9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>1.43</v>
       </c>
       <c r="BZ9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-11 18:44:38</t>
+          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.74</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.58</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>1.48</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 21:00:43</t>
+          <t>2026-07-11 23:16:41</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>1.28</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J3" t="n">
         <v>6.8</v>
@@ -1135,40 +1135,40 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Z3" t="n">
         <v>150</v>
@@ -1180,10 +1180,10 @@
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AD3" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AE3" t="n">
         <v>240</v>
@@ -1192,43 +1192,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AO3" t="n">
         <v>300</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>8.800000000000001</v>
@@ -1237,10 +1237,10 @@
         <v>13.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
@@ -1249,10 +1249,10 @@
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1261,80 +1261,80 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT3" t="n">
         <v>17</v>
       </c>
-      <c r="BK3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>22</v>
-      </c>
       <c r="BU3" t="n">
-        <v>1.91</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.08</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="CA3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 21:00:43</t>
+          <t>2026-07-11 23:16:41</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
         <v>1.89</v>
@@ -1374,13 +1374,13 @@
         <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.1</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="S4" t="n">
-        <v>1.07</v>
+        <v>1.79</v>
       </c>
       <c r="T4" t="n">
         <v>1.4</v>
@@ -1413,118 +1413,118 @@
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
         <v>2.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 21:00:43</t>
+          <t>2026-07-11 23:16:41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>1.19</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 21:00:43</t>
+          <t>2026-07-11 23:16:41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.58</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.41</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY6" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ6" t="n">
+      <c r="BK6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
+      <c r="BR6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS6" t="n">
         <v>11</v>
       </c>
-      <c r="BN6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BT6" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 21:00:43</t>
+          <t>2026-07-11 23:16:41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="G7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>2.94</v>
       </c>
       <c r="J7" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 21:00:43</t>
+          <t>2026-07-11 23:16:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.95</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>2.68</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>3.15</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
         <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.98</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF8" t="n">
         <v>22</v>
       </c>
-      <c r="AE8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12</v>
-      </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>11</v>
-      </c>
       <c r="AR8" t="n">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT8" t="n">
         <v>7</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>6</v>
       </c>
-      <c r="AU8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10</v>
-      </c>
       <c r="BN8" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW8" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 21:00:43</t>
+          <t>2026-07-11 23:16:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,239 +2626,493 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G9" t="n">
         <v>2.04</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.4</v>
-      </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
         <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>50</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-11 23:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.47</v>
       </c>
-      <c r="T9" t="n">
+      <c r="P10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.99</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="U10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.71</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X10" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y10" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z10" t="n">
         <v>32</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA10" t="n">
         <v>110</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AD10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="n">
         <v>75</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF10" t="n">
         <v>16.5</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG10" t="n">
         <v>14</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AH10" t="n">
         <v>27</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AI10" t="n">
         <v>95</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AJ10" t="n">
         <v>40</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK10" t="n">
         <v>38</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AL10" t="n">
         <v>70</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AM10" t="n">
         <v>200</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AN10" t="n">
         <v>38</v>
       </c>
-      <c r="AO9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="AO10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP10" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF10" t="n">
         <v>21</v>
       </c>
-      <c r="AS9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BG10" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH9" t="n">
+      <c r="BH10" t="n">
         <v>3.4</v>
       </c>
-      <c r="BI9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
         <v>1.43</v>
       </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>1.43</v>
       </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
         <v>1.43</v>
       </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>1.43</v>
       </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
         <v>1.43</v>
       </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
         <v>1.43</v>
       </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
         <v>1.43</v>
       </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>1.43</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>1.43</v>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-07-11 21:00:43</t>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-11 23:16:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>
@@ -1144,10 +1144,10 @@
         <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
         <v>2.28</v>
@@ -1159,7 +1159,7 @@
         <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
         <v>4.5</v>
@@ -1183,7 +1183,7 @@
         <v>17</v>
       </c>
       <c r="AD3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AE3" t="n">
         <v>240</v>
@@ -1219,16 +1219,16 @@
         <v>300</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>8.800000000000001</v>
@@ -1240,7 +1240,7 @@
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
@@ -1249,10 +1249,10 @@
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1264,13 +1264,13 @@
         <v>7.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3" t="n">
         <v>4.9</v>
@@ -1330,11 +1330,11 @@
         <v>9.6</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1527,68 +1527,68 @@
         <v>14.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM4" t="n">
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1646,19 +1646,19 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T6" t="n">
         <v>1.9</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>3.45</v>
@@ -2136,7 +2136,7 @@
         <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J7" t="n">
         <v>2.98</v>
@@ -2145,19 +2145,19 @@
         <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q7" t="n">
         <v>2.5</v>
@@ -2172,10 +2172,10 @@
         <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
         <v>1.41</v>
@@ -2187,7 +2187,7 @@
         <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>60</v>
@@ -2202,7 +2202,7 @@
         <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="n">
         <v>25</v>
@@ -2223,16 +2223,16 @@
         <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
         <v>75</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
         <v>6.6</v>
@@ -2244,10 +2244,10 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
         <v>6</v>
@@ -2256,7 +2256,7 @@
         <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX7" t="n">
         <v>14.5</v>
@@ -2268,43 +2268,43 @@
         <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4</v>
       </c>
       <c r="BG7" t="n">
         <v>4</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,22 +2316,22 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU7" t="n">
         <v>4.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
         <v>8.199999999999999</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T8" t="n">
         <v>1.98</v>
@@ -2432,7 +2432,7 @@
         <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
         <v>9.6</v>
@@ -2468,7 +2468,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
         <v>65</v>
@@ -2498,7 +2498,7 @@
         <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2510,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX8" t="n">
         <v>14.5</v>
@@ -2528,19 +2528,19 @@
         <v>5.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE8" t="n">
         <v>5.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="n">
         <v>2.88</v>
@@ -2582,7 +2582,7 @@
         <v>6</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>7.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
         <v>8.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
@@ -2683,7 +2683,7 @@
         <v>1.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
         <v>1.96</v>
@@ -2692,22 +2692,22 @@
         <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
         <v>42</v>
       </c>
       <c r="AA9" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
         <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>95</v>
@@ -2725,7 +2725,7 @@
         <v>120</v>
       </c>
       <c r="AJ9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
         <v>32</v>
@@ -2734,13 +2734,13 @@
         <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO9" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP9" t="n">
         <v>7.4</v>
@@ -2749,10 +2749,10 @@
         <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2764,7 +2764,7 @@
         <v>17</v>
       </c>
       <c r="AW9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
         <v>9.800000000000001</v>
@@ -2776,7 +2776,7 @@
         <v>19.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
         <v>19.5</v>
@@ -2788,19 +2788,19 @@
         <v>42</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF9" t="n">
         <v>17.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ9" t="n">
         <v>12</v>
@@ -2812,13 +2812,13 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
         <v>4.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BP9" t="n">
         <v>16</v>
@@ -2830,7 +2830,7 @@
         <v>50</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>8.4</v>
@@ -2842,23 +2842,23 @@
         <v>65</v>
       </c>
       <c r="BW9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX9" t="n">
         <v>90</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
         <v>50</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
@@ -2934,7 +2934,7 @@
         <v>1.99</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
         <v>1.31</v>
@@ -3051,68 +3051,68 @@
         <v>4.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.43</v>
+        <v>5.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.43</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.43</v>
+        <v>3.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.43</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.43</v>
+        <v>8.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.43</v>
+        <v>5.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.43</v>
+        <v>8.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.43</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-11 23:16:41</t>
+          <t>2026-07-12 01:32:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,19 +875,19 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
         <v>1.87</v>
@@ -896,10 +896,10 @@
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
         <v>2.02</v>
@@ -923,7 +923,7 @@
         <v>140</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>9.4</v>
@@ -965,22 +965,22 @@
         <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>5.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>4.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
@@ -1007,7 +1007,7 @@
         <v>6</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
         <v>8</v>
@@ -1016,71 +1016,71 @@
         <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP2" t="n">
         <v>13</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR2" t="n">
         <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY2" t="n">
         <v>2.56</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>2.58</v>
       </c>
       <c r="BZ2" t="n">
         <v>23</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
         <v>6.8</v>
@@ -1135,25 +1135,25 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
         <v>1.96</v>
@@ -1174,13 +1174,13 @@
         <v>150</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>650</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD3" t="n">
         <v>55</v>
@@ -1189,7 +1189,7 @@
         <v>240</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1201,7 +1201,7 @@
         <v>180</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK3" t="n">
         <v>14</v>
@@ -1210,28 +1210,28 @@
         <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AO3" t="n">
         <v>300</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT3" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
         <v>13.5</v>
@@ -1240,19 +1240,19 @@
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>9</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BA3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1261,25 +1261,25 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK3" t="n">
         <v>5.9</v>
@@ -1288,13 +1288,13 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP3" t="n">
         <v>7</v>
@@ -1303,45 +1303,45 @@
         <v>5.1</v>
       </c>
       <c r="BR3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS3" t="n">
         <v>7.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>9.6</v>
       </c>
       <c r="CA3" t="n">
         <v>5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>7.8</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="R4" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,33 +1605,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.02</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.29</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>17</v>
       </c>
-      <c r="AE6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="BC6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="BD6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU6" t="n">
+      <c r="BQ6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW6" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY6" t="n">
+      <c r="BX6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>30</v>
-      </c>
       <c r="CA6" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.92</v>
+        <v>2.24</v>
       </c>
       <c r="J7" t="n">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="U7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.8</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.52</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="CA7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>2.06</v>
       </c>
       <c r="H8" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="X8" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
         <v>21</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AK8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG8" t="n">
         <v>50</v>
       </c>
-      <c r="AL8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="BH8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT8" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW8" t="n">
+      <c r="BU8" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="BV8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>8.6</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,244 +2621,244 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>2.92</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
         <v>1.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR9" t="n">
         <v>12</v>
       </c>
-      <c r="Y9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AS9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT9" t="n">
         <v>8</v>
       </c>
-      <c r="AD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR9" t="n">
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN9" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="BO9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>65</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>90</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>10</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
@@ -2875,244 +2875,752 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.47</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.31</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI10" t="n">
         <v>75</v>
       </c>
-      <c r="AF10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>95</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN10" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>19</v>
+        <v>4.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>5.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
         <v>8.6</v>
       </c>
       <c r="BT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>50</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-12 03:48:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS11" t="n">
         <v>7.2</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="AT11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-12 03:48:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN12" t="n">
         <v>5.1</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="BO12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV12" t="n">
         <v>38</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="BW12" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="BX12" t="n">
         <v>60</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="BY12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="BZ12" t="n">
         <v>44</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CA12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-07-12 01:32:45</t>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -860,13 +860,13 @@
         <v>1.74</v>
       </c>
       <c r="G2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -887,7 +887,7 @@
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
         <v>1.87</v>
@@ -899,13 +899,13 @@
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
         <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
         <v>2.1</v>
@@ -1019,22 +1019,22 @@
         <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1058,10 +1058,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW2" t="n">
         <v>2.54</v>
@@ -1070,7 +1070,7 @@
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BZ2" t="n">
         <v>23</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J3" t="n">
         <v>6.8</v>
@@ -1144,16 +1144,16 @@
         <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
         <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
         <v>1.96</v>
@@ -1174,7 +1174,7 @@
         <v>150</v>
       </c>
       <c r="AA3" t="n">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
@@ -1183,7 +1183,7 @@
         <v>16.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE3" t="n">
         <v>240</v>
@@ -1225,10 +1225,10 @@
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1240,19 +1240,19 @@
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX3" t="n">
         <v>7.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>9</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1264,13 +1264,13 @@
         <v>9</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
         <v>1.04</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.03</v>
@@ -1658,7 +1658,7 @@
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>1.73</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="n">
         <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
         <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.17</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.1</v>
@@ -1912,7 +1912,7 @@
         <v>2.02</v>
       </c>
       <c r="S6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="T6" t="n">
         <v>1.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="G7" t="n">
         <v>3.65</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
         <v>1.58</v>
@@ -2166,13 +2166,13 @@
         <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="T7" t="n">
         <v>1.56</v>
       </c>
       <c r="U7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
         <v>1.8</v>
@@ -2235,43 +2235,43 @@
         <v>13</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
         <v>1.03</v>
@@ -2280,7 +2280,7 @@
         <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>17</v>
@@ -2292,65 +2292,65 @@
         <v>4.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>30</v>
       </c>
       <c r="BS7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
         <v>5.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>14.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>23</v>
       </c>
       <c r="BY7" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>16.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -2408,7 +2408,7 @@
         <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
         <v>1.83</v>
@@ -2429,40 +2429,40 @@
         <v>1.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
@@ -2471,10 +2471,10 @@
         <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
         <v>42</v>
@@ -2483,7 +2483,7 @@
         <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>70</v>
@@ -2495,10 +2495,10 @@
         <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AT8" t="n">
         <v>7.6</v>
@@ -2510,7 +2510,7 @@
         <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2534,10 +2534,10 @@
         <v>36</v>
       </c>
       <c r="BE8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF8" t="n">
         <v>15</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>15.5</v>
       </c>
       <c r="BG8" t="n">
         <v>50</v>
@@ -2570,7 +2570,7 @@
         <v>15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>32</v>
@@ -2585,7 +2585,7 @@
         <v>5.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
         <v>11.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>2.98</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.46</v>
@@ -2704,7 +2704,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
         <v>16</v>
@@ -2752,7 +2752,7 @@
         <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
@@ -2764,7 +2764,7 @@
         <v>9.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2776,25 +2776,25 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH9" t="n">
         <v>2.82</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -2898,13 +2898,13 @@
         <v>2.68</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
         <v>2.86</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.48</v>
@@ -2916,19 +2916,19 @@
         <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
@@ -2943,7 +2943,7 @@
         <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y10" t="n">
         <v>9</v>
@@ -3003,52 +3003,52 @@
         <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AY10" t="n">
         <v>4.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE10" t="n">
         <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="n">
         <v>2.88</v>
@@ -3099,20 +3099,20 @@
         <v>7.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
         <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
         <v>8.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -3191,10 +3191,10 @@
         <v>1.81</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
@@ -3248,7 +3248,7 @@
         <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP11" t="n">
         <v>7.4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
@@ -3430,7 +3430,7 @@
         <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -3442,7 +3442,7 @@
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
@@ -3463,7 +3463,7 @@
         <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC12" t="n">
         <v>8.800000000000001</v>
@@ -3505,70 +3505,70 @@
         <v>100</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU12" t="n">
         <v>5.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BA12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB12" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB12" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BC12" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ12" t="n">
         <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3583,7 +3583,7 @@
         <v>3.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ12" t="n">
         <v>7</v>
@@ -3613,14 +3613,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CA12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>1.48</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>1.28</v>
       </c>
       <c r="H3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
         <v>6.8</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1135,13 +1135,13 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q3" t="n">
         <v>1.51</v>
@@ -1153,22 +1153,22 @@
         <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z3" t="n">
         <v>150</v>
@@ -1201,7 +1201,7 @@
         <v>180</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK3" t="n">
         <v>14</v>
@@ -1219,19 +1219,19 @@
         <v>300</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR3" t="n">
         <v>10</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>11</v>
       </c>
-      <c r="AS3" t="n">
-        <v>12</v>
-      </c>
       <c r="AT3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU3" t="n">
         <v>13.5</v>
@@ -1240,19 +1240,19 @@
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX3" t="n">
         <v>7.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1261,16 +1261,16 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,33 +1351,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="S4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1646,19 +1646,19 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="P5" t="n">
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.73</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>7.8</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="P6" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="R6" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="G7" t="n">
-        <v>3.65</v>
+        <v>1.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.06</v>
+        <v>3.75</v>
       </c>
       <c r="I7" t="n">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="S7" t="n">
-        <v>2.46</v>
+        <v>1.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="Y7" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB7" t="n">
         <v>17</v>
       </c>
-      <c r="Z7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW7" t="n">
+      <c r="BC7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>8</v>
-      </c>
       <c r="BH7" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BJ7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW7" t="n">
         <v>7.2</v>
       </c>
-      <c r="BO7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BX7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.99</v>
+        <v>3.95</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="H8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J8" t="n">
         <v>4.2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>4.5</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>3.95</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>2.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN8" t="n">
         <v>32</v>
       </c>
-      <c r="AA8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>17</v>
-      </c>
       <c r="AO8" t="n">
-        <v>70</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AS8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY8" t="n">
         <v>15</v>
       </c>
-      <c r="AT8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BD8" t="n">
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BG8" t="n">
-        <v>50</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8" t="n">
         <v>32</v>
       </c>
       <c r="BS8" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY8" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="G9" t="n">
-        <v>3.45</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.92</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP9" t="n">
         <v>11</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA9" t="n">
         <v>10</v>
       </c>
-      <c r="Z9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.3</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>48</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>75</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>65</v>
-      </c>
       <c r="AK10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO10" t="n">
         <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
       </c>
       <c r="AV10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AX10" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA10" t="n">
         <v>4.5</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BB10" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.84</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>1.02</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
@@ -3383,244 +3383,752 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>2.82</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
         <v>8</v>
       </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI12" t="n">
         <v>75</v>
       </c>
-      <c r="AF12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>95</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN12" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA12" t="n">
         <v>5.7</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BB12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC12" t="n">
         <v>5.5</v>
       </c>
-      <c r="AV12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="BJ12" t="n">
         <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
         <v>8.6</v>
       </c>
       <c r="BT12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-12 08:21:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS13" t="n">
         <v>7.2</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="AT13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-12 08:21:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN14" t="n">
         <v>5.1</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="BO14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV14" t="n">
         <v>38</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="BW14" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="BX14" t="n">
         <v>60</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="BY14" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="BZ14" t="n">
         <v>46</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CA14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-07-12 06:05:18</t>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -878,10 +878,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>1.28</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I3" t="n">
         <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>7.4</v>
@@ -1144,7 +1144,7 @@
         <v>2.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.69</v>
@@ -1162,7 +1162,7 @@
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
@@ -1198,10 +1198,10 @@
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK3" t="n">
         <v>14</v>
@@ -1216,22 +1216,22 @@
         <v>4.1</v>
       </c>
       <c r="AO3" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AP3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
         <v>13.5</v>
@@ -1240,19 +1240,19 @@
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
         <v>7.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1264,13 +1264,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
         <v>3.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -1365,145 +1365,145 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
@@ -1521,22 +1521,22 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>14.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="I8" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
@@ -2423,16 +2423,16 @@
         <v>2.42</v>
       </c>
       <c r="T8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X8" t="n">
         <v>25</v>
@@ -2447,7 +2447,7 @@
         <v>24</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC8" t="n">
         <v>11.5</v>
@@ -2456,34 +2456,34 @@
         <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
         <v>26</v>
       </c>
       <c r="AJ8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
         <v>46</v>
       </c>
       <c r="AM8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO8" t="n">
         <v>9.800000000000001</v>
@@ -2492,25 +2492,25 @@
         <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AS8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AT8" t="n">
         <v>18.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX8" t="n">
         <v>29</v>
@@ -2525,7 +2525,7 @@
         <v>22</v>
       </c>
       <c r="BB8" t="n">
-        <v>60</v>
+        <v>6.2</v>
       </c>
       <c r="BC8" t="n">
         <v>34</v>
@@ -2534,13 +2534,13 @@
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BF8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
         <v>4.4</v>
@@ -2549,10 +2549,10 @@
         <v>3.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,34 +2561,34 @@
         <v>11.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BP8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BQ8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS8" t="n">
         <v>9.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX8" t="n">
         <v>22</v>
@@ -2597,14 +2597,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
         <v>4.6</v>
@@ -2686,7 +2686,7 @@
         <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
         <v>13</v>
@@ -2737,7 +2737,7 @@
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>75</v>
@@ -2758,7 +2758,7 @@
         <v>7.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
         <v>15.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I10" t="n">
         <v>2.92</v>
@@ -2904,7 +2904,7 @@
         <v>2.98</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.46</v>
@@ -2913,13 +2913,13 @@
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O10" t="n">
         <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q10" t="n">
         <v>2.5</v>
@@ -2931,16 +2931,16 @@
         <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
         <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
         <v>11</v>
@@ -2976,19 +2976,19 @@
         <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>75</v>
       </c>
       <c r="AK10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL10" t="n">
         <v>85</v>
       </c>
       <c r="AM10" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN10" t="n">
         <v>70</v>
@@ -2997,7 +2997,7 @@
         <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>7.2</v>
@@ -3006,7 +3006,7 @@
         <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
@@ -3036,28 +3036,28 @@
         <v>4.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.4</v>
       </c>
       <c r="BH10" t="n">
         <v>2.82</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
         <v>6</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN10" t="n">
         <v>6.2</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
         <v>5.6</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -3143,145 +3143,145 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>2.98</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
         <v>1.03</v>
@@ -3299,22 +3299,22 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,50 +3323,50 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>2.82</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
         <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J12" t="n">
         <v>2.86</v>
@@ -3613,14 +3613,14 @@
         <v>8.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA12" t="n">
         <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="G13" t="n">
         <v>2.06</v>
@@ -3675,31 +3675,31 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
         <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R13" t="n">
         <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
         <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>1.96</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
         <v>2.4</v>
@@ -3917,46 +3917,46 @@
         <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O14" t="n">
         <v>1.47</v>
       </c>
       <c r="P14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
         <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X14" t="n">
         <v>11.5</v>
@@ -3968,7 +3968,7 @@
         <v>32</v>
       </c>
       <c r="AA14" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB14" t="n">
         <v>8</v>
@@ -3977,10 +3977,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF14" t="n">
         <v>16.5</v>
@@ -3989,94 +3989,94 @@
         <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK14" t="n">
         <v>38</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF14" t="n">
         <v>4.3</v>
       </c>
-      <c r="BE14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4085,50 +4085,50 @@
         <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO14" t="n">
         <v>3.8</v>
       </c>
       <c r="BP14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ14" t="n">
         <v>7</v>
       </c>
       <c r="BR14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS14" t="n">
         <v>8.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU14" t="n">
         <v>5.1</v>
       </c>
       <c r="BV14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW14" t="n">
         <v>8.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="CA14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
@@ -884,7 +884,7 @@
         <v>1.58</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
         <v>1.57</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.82</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
@@ -1123,40 +1123,40 @@
         <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
@@ -1165,10 +1165,10 @@
         <v>4.5</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Y3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z3" t="n">
         <v>150</v>
@@ -1177,28 +1177,28 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE3" t="n">
         <v>240</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
         <v>10.5</v>
@@ -1210,49 +1210,49 @@
         <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
         <v>4.1</v>
       </c>
       <c r="AO3" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT3" t="n">
         <v>10</v>
       </c>
-      <c r="AR3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AU3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AV3" t="n">
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1261,16 +1261,16 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
         <v>5</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,154 +1356,154 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>CA Fenix</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>5.6</v>
+        <v>1.61</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
@@ -1521,22 +1521,22 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,57 +1545,57 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,159 +1605,159 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>CA Claypole</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Leones de Rosario</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.05</v>
+        <v>2.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
@@ -1775,81 +1775,81 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,159 +1859,159 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>5.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
         <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
         <v>1.03</v>
@@ -2029,22 +2029,22 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,57 +2053,57 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.73</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>7.8</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="G8" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>1.87</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.42</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="H9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>4.6</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>2.02</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>1.78</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="Y9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG9" t="n">
         <v>14</v>
       </c>
-      <c r="Z9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AH9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN9" t="n">
+      <c r="BN9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR9" t="n">
         <v>17</v>
       </c>
-      <c r="AO9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR9" t="n">
+      <c r="BS9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV9" t="n">
         <v>27</v>
       </c>
-      <c r="AS9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BW9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>30</v>
-      </c>
       <c r="CA9" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2.92</v>
+        <v>1.86</v>
       </c>
       <c r="J10" t="n">
-        <v>2.98</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>2.68</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>2.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>48</v>
+        <v>19.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AG10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
         <v>26</v>
       </c>
-      <c r="AI10" t="n">
-        <v>65</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK10" t="n">
         <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="AN10" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN10" t="n">
         <v>8</v>
       </c>
-      <c r="AU10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BO10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY10" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.65</v>
       </c>
-      <c r="G11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO11" t="n">
         <v>4.1</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="BP11" t="n">
         <v>15</v>
       </c>
-      <c r="AC11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="BQ11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR11" t="n">
         <v>32</v>
       </c>
-      <c r="AF11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>50</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK11" t="n">
+      <c r="BS11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT11" t="n">
         <v>7.6</v>
       </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>38</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BR11" t="n">
+      <c r="BU11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX11" t="n">
         <v>55</v>
       </c>
-      <c r="BS11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BW11" t="n">
+      <c r="BY11" t="n">
         <v>12.5</v>
       </c>
-      <c r="BX11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>25</v>
-      </c>
       <c r="BZ11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="CA11" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N12" t="n">
         <v>2.68</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.66</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
         <v>48</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>75</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>65</v>
-      </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
         <v>180</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD12" t="n">
         <v>4.8</v>
       </c>
-      <c r="AY12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
         <v>6</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT12" t="n">
         <v>5.6</v>
       </c>
-      <c r="BG12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>28</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6</v>
-      </c>
       <c r="BU12" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.99</v>
+        <v>3.65</v>
       </c>
       <c r="G13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H13" t="n">
         <v>2.06</v>
       </c>
-      <c r="H13" t="n">
-        <v>4.7</v>
-      </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>2.24</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>21</v>
-      </c>
       <c r="AE13" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>34</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>36</v>
+      </c>
+      <c r="CA13" t="n">
         <v>24</v>
       </c>
-      <c r="AK13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>9.4</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
@@ -3891,192 +3891,192 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
         <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC14" t="n">
         <v>8</v>
       </c>
-      <c r="AC14" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW14" t="n">
         <v>5.6</v>
       </c>
-      <c r="AV14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AX14" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4085,50 +4085,558 @@
         <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
         <v>8.6</v>
       </c>
       <c r="BT14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>48</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-12 12:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW15" t="n">
         <v>7</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="AX15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-12 12:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS16" t="n">
         <v>5.1</v>
       </c>
-      <c r="BV14" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW14" t="n">
+      <c r="AT16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW16" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
+      <c r="BX16" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>42</v>
-      </c>
-      <c r="CA14" t="n">
+      <c r="BZ16" t="n">
+        <v>44</v>
+      </c>
+      <c r="CA16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-07-12 10:37:00</t>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>2.22</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
@@ -890,13 +890,13 @@
         <v>1.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.26</v>
       </c>
       <c r="G3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="I3" t="n">
         <v>15</v>
@@ -1141,37 +1141,37 @@
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="X3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1180,103 +1180,103 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD3" t="n">
         <v>48</v>
       </c>
       <c r="AE3" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL3" t="n">
         <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AO3" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV3" t="n">
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="BH3" t="n">
         <v>5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>13</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1395,10 +1395,10 @@
         <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.88</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H5" t="n">
         <v>2.78</v>
@@ -1634,7 +1634,7 @@
         <v>2.68</v>
       </c>
       <c r="K5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.55</v>
@@ -1670,7 +1670,7 @@
         <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
         <v>8.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="X6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF6" t="n">
         <v>13</v>
       </c>
-      <c r="Z6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>15</v>
-      </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
         <v>32</v>
       </c>
       <c r="AI6" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
         <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AP6" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
         <v>8</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AY6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
         <v>20</v>
       </c>
-      <c r="AS6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="BG6" t="n">
+        <v>110</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>80</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ6" t="n">
+      <c r="BK6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>14.5</v>
       </c>
       <c r="BR6" t="n">
         <v>48</v>
       </c>
       <c r="BS6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BW6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BZ6" t="n">
         <v>55</v>
       </c>
       <c r="CA6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -2127,46 +2127,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -2393,34 +2393,34 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.03</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
         <v>1.03</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.17</v>
@@ -2659,154 +2659,154 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
         <v>1.78</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="X9" t="n">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z9" t="n">
         <v>55</v>
       </c>
       <c r="AA9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
         <v>16</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
         <v>38</v>
       </c>
       <c r="AJ9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP9" t="n">
         <v>27</v>
       </c>
-      <c r="AK9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="AQ9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE9" t="n">
         <v>24</v>
       </c>
-      <c r="AM9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="BF9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI9" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="BJ9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK9" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4.6</v>
       </c>
       <c r="BL9" t="n">
         <v>55</v>
@@ -2815,50 +2815,50 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY9" t="n">
         <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.86</v>
       </c>
       <c r="J10" t="n">
         <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
@@ -2919,200 +2919,200 @@
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB10" t="n">
         <v>25</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE10" t="n">
         <v>16</v>
       </c>
-      <c r="Z10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG10" t="n">
         <v>19.5</v>
       </c>
-      <c r="AF10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
         <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="n">
         <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN10" t="n">
         <v>44</v>
       </c>
       <c r="AO10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ10" t="n">
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BD10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG10" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7</v>
-      </c>
       <c r="BH10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI10" t="n">
         <v>3.4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO10" t="n">
         <v>5.3</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5</v>
-      </c>
       <c r="BP10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BR10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA10" t="n">
         <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
         <v>3.55</v>
@@ -3170,7 +3170,7 @@
         <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
         <v>1.83</v>
@@ -3182,7 +3182,7 @@
         <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
         <v>1.91</v>
@@ -3191,10 +3191,10 @@
         <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
@@ -3209,7 +3209,7 @@
         <v>100</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7.8</v>
@@ -3260,19 +3260,19 @@
         <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
         <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3296,7 +3296,7 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BF11" t="n">
         <v>15</v>
@@ -3359,14 +3359,14 @@
         <v>12.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
         <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="I13" t="n">
         <v>2.24</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
         <v>1.46</v>
@@ -3678,10 +3678,10 @@
         <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
         <v>2.16</v>
@@ -3693,25 +3693,25 @@
         <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V13" t="n">
         <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
         <v>32</v>
@@ -3720,10 +3720,10 @@
         <v>15</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>32</v>
@@ -3756,40 +3756,40 @@
         <v>85</v>
       </c>
       <c r="AO13" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AP13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AW13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX13" t="n">
         <v>19</v>
       </c>
-      <c r="AX13" t="n">
-        <v>20</v>
-      </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>28</v>
@@ -3798,7 +3798,7 @@
         <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
         <v>1.03</v>
@@ -3807,10 +3807,10 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BG13" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH13" t="n">
         <v>3.15</v>
@@ -3831,40 +3831,40 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BR13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX13" t="n">
         <v>36</v>
       </c>
       <c r="BY13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BZ13" t="n">
         <v>36</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>3.25</v>
       </c>
       <c r="H14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I14" t="n">
         <v>3.1</v>
@@ -4025,7 +4025,7 @@
         <v>5.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
@@ -4088,7 +4088,7 @@
         <v>6</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
         <v>28</v>
@@ -4115,27 +4115,27 @@
         <v>7.6</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
         <v>8.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
         <v>8.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,498 +4145,1006 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Betim Futebol</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>1.24</v>
       </c>
       <c r="O15" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.42</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Brazilian Serie D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>America RN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Trem AP</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:04:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:04:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Figueirense</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="F18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G18" t="n">
         <v>2.4</v>
       </c>
-      <c r="H16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="H18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I18" t="n">
         <v>4.2</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K18" t="n">
         <v>3.35</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="L18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M18" t="n">
         <v>1.11</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N18" t="n">
         <v>2.76</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O18" t="n">
         <v>1.47</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="P18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S18" t="n">
         <v>4.7</v>
       </c>
-      <c r="T16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.31</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W18" t="n">
         <v>1.72</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X18" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y18" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z18" t="n">
         <v>32</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA18" t="n">
         <v>100</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB18" t="n">
         <v>8</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD18" t="n">
         <v>20</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE18" t="n">
         <v>70</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AF18" t="n">
         <v>16.5</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG18" t="n">
         <v>14</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH18" t="n">
         <v>26</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AI18" t="n">
         <v>90</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AJ18" t="n">
         <v>40</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK18" t="n">
         <v>38</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AL18" t="n">
         <v>65</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AM18" t="n">
         <v>190</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AN18" t="n">
         <v>36</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AO18" t="n">
         <v>90</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AP18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT18" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS16" t="n">
+      <c r="BU18" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV16" t="n">
+      <c r="BV18" t="n">
         <v>38</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="BW18" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="BX18" t="n">
         <v>60</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="BY18" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="BZ18" t="n">
         <v>44</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CA18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-07-12 12:51:08</t>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -884,19 +884,19 @@
         <v>2.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
         <v>1.27</v>
       </c>
       <c r="H3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
         <v>15</v>
@@ -1129,19 +1129,19 @@
         <v>7.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q3" t="n">
         <v>1.5</v>
@@ -1150,31 +1150,31 @@
         <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB3" t="n">
         <v>11.5</v>
@@ -1195,37 +1195,37 @@
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AK3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL3" t="n">
         <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS3" t="n">
         <v>55</v>
@@ -1237,7 +1237,7 @@
         <v>14</v>
       </c>
       <c r="AV3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW3" t="n">
         <v>46</v>
@@ -1246,43 +1246,43 @@
         <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BE3" t="n">
         <v>44</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
         <v>5</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3" t="n">
         <v>13</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1306,7 +1306,7 @@
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
         <v>16.5</v>
@@ -1324,17 +1324,17 @@
         <v>90</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA3" t="n">
         <v>5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="G5" t="n">
         <v>3.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
         <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="K5" t="n">
         <v>3.1</v>
@@ -1658,7 +1658,7 @@
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
@@ -1670,7 +1670,7 @@
         <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
         <v>8.6</v>
@@ -1727,37 +1727,37 @@
         <v>90</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
@@ -1775,10 +1775,10 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
         <v>2.56</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
         <v>5.7</v>
@@ -1924,7 +1924,7 @@
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X6" t="n">
         <v>10</v>
@@ -1933,10 +1933,10 @@
         <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB6" t="n">
         <v>7.8</v>
@@ -1963,10 +1963,10 @@
         <v>150</v>
       </c>
       <c r="AJ6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
         <v>80</v>
@@ -1975,7 +1975,7 @@
         <v>280</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO6" t="n">
         <v>200</v>
@@ -1984,7 +1984,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>1.03</v>
@@ -1996,7 +1996,7 @@
         <v>4.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>15.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -2127,118 +2127,118 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="P7" t="n">
         <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
         <v>1.03</v>
@@ -2247,55 +2247,55 @@
         <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
         <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BG7" t="n">
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BI7" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
@@ -2307,25 +2307,25 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO7" t="n">
         <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU7" t="n">
         <v>1.01</v>
@@ -2343,14 +2343,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="CA7" t="n">
         <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -2381,166 +2381,166 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>5.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>1.54</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H9" t="n">
         <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
         <v>5.3</v>
@@ -2659,37 +2659,37 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="T9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V9" t="n">
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X9" t="n">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="Y9" t="n">
         <v>38</v>
@@ -2707,22 +2707,22 @@
         <v>14.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>46</v>
       </c>
       <c r="AF9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
         <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
         <v>22</v>
@@ -2731,25 +2731,25 @@
         <v>15.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ9" t="n">
         <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS9" t="n">
         <v>60</v>
@@ -2758,16 +2758,16 @@
         <v>18</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
@@ -2776,7 +2776,7 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
         <v>17.5</v>
@@ -2785,34 +2785,34 @@
         <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BE9" t="n">
         <v>24</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH9" t="n">
         <v>6.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL9" t="n">
         <v>55</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BN9" t="n">
         <v>5.6</v>
@@ -2824,10 +2824,10 @@
         <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BS9" t="n">
         <v>6</v>
@@ -2836,29 +2836,29 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV9" t="n">
         <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX9" t="n">
         <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J10" t="n">
         <v>4.3</v>
@@ -2907,7 +2907,7 @@
         <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
@@ -2922,13 +2922,13 @@
         <v>2.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
         <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.62</v>
@@ -2937,10 +2937,10 @@
         <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
@@ -2955,7 +2955,7 @@
         <v>19.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="n">
         <v>11</v>
@@ -2967,7 +2967,7 @@
         <v>16</v>
       </c>
       <c r="AF10" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AG10" t="n">
         <v>19.5</v>
@@ -2979,25 +2979,25 @@
         <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AK10" t="n">
         <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO10" t="n">
         <v>7.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>11</v>
@@ -3006,10 +3006,10 @@
         <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU10" t="n">
         <v>9.4</v>
@@ -3018,7 +3018,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX10" t="n">
         <v>36</v>
@@ -3027,7 +3027,7 @@
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>22</v>
@@ -3039,13 +3039,13 @@
         <v>36</v>
       </c>
       <c r="BD10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF10" t="n">
         <v>34</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>17.5</v>
       </c>
       <c r="BG10" t="n">
         <v>6.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G11" t="n">
         <v>2.04</v>
@@ -3152,10 +3152,10 @@
         <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
@@ -3170,7 +3170,7 @@
         <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
         <v>1.83</v>
@@ -3182,19 +3182,19 @@
         <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
         <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -3762,34 +3762,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AX13" t="n">
         <v>19</v>
       </c>
       <c r="AY13" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
         <v>28</v>
@@ -3810,7 +3810,7 @@
         <v>48</v>
       </c>
       <c r="BG13" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BH13" t="n">
         <v>3.15</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
         <v>4.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
         <v>1.83</v>
@@ -4016,7 +4016,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
         <v>4.8</v>
@@ -4025,7 +4025,7 @@
         <v>5.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
@@ -4088,7 +4088,7 @@
         <v>6</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP14" t="n">
         <v>28</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
         <v>1.48</v>
@@ -4706,13 +4706,13 @@
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T17" t="n">
         <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V17" t="n">
         <v>1.25</v>
@@ -4805,7 +4805,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="BA17" t="n">
         <v>7.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -4960,13 +4960,13 @@
         <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V18" t="n">
         <v>1.31</v>
@@ -5041,10 +5041,10 @@
         <v>5.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
         <v>12</v>
@@ -5053,10 +5053,10 @@
         <v>5</v>
       </c>
       <c r="AX18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY18" t="n">
         <v>10</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>16</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -860,28 +860,28 @@
         <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -893,10 +893,10 @@
         <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -908,10 +908,10 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -923,10 +923,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -935,10 +935,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -947,76 +947,76 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H3" t="n">
         <v>13</v>
@@ -1135,13 +1135,13 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
         <v>1.5</v>
@@ -1150,28 +1150,28 @@
         <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
         <v>60</v>
       </c>
       <c r="Z3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>690</v>
@@ -1180,7 +1180,7 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
         <v>48</v>
@@ -1201,10 +1201,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AL3" t="n">
         <v>36</v>
@@ -1213,22 +1213,22 @@
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AO3" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR3" t="n">
         <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1264,7 +1264,7 @@
         <v>29</v>
       </c>
       <c r="BE3" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BF3" t="n">
         <v>3.7</v>
@@ -1276,7 +1276,7 @@
         <v>5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>13</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
@@ -1398,25 +1398,25 @@
         <v>1.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.61</v>
+        <v>6.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1425,106 +1425,106 @@
         <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
         <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J5" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="K5" t="n">
         <v>3.1</v>
@@ -1658,7 +1658,7 @@
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
@@ -1670,10 +1670,10 @@
         <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Y5" t="n">
         <v>9.4</v>
@@ -1682,16 +1682,16 @@
         <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AB5" t="n">
         <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>65</v>
@@ -1703,61 +1703,61 @@
         <v>18.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="AK5" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AL5" t="n">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AM5" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
@@ -1775,10 +1775,10 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="n">
         <v>2.56</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
@@ -1927,40 +1927,40 @@
         <v>1.84</v>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>26</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="AJ6" t="n">
         <v>29</v>
@@ -1969,31 +1969,31 @@
         <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
         <v>30</v>
       </c>
       <c r="AO6" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
@@ -2002,7 +2002,7 @@
         <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -2014,7 +2014,7 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB6" t="n">
         <v>19</v>
@@ -2023,16 +2023,16 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>110</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="n">
         <v>2.86</v>
@@ -2044,7 +2044,7 @@
         <v>13.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2062,41 +2062,41 @@
         <v>19.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>48</v>
       </c>
       <c r="BS6" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>60</v>
       </c>
       <c r="BW6" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>85</v>
       </c>
       <c r="BY6" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>55</v>
       </c>
       <c r="CA6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -2133,10 +2133,10 @@
         <v>1.48</v>
       </c>
       <c r="H7" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.05</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>1.08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q7" t="n">
         <v>1.25</v>
@@ -2178,13 +2178,13 @@
         <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y7" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="Z7" t="n">
         <v>110</v>
@@ -2199,25 +2199,25 @@
         <v>22</v>
       </c>
       <c r="AD7" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF7" t="n">
         <v>19.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
@@ -2229,128 +2229,128 @@
         <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="n">
         <v>7</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BN7" t="n">
         <v>5.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP7" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR7" t="n">
         <v>16</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BT7" t="n">
         <v>13</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
         <v>7.4</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G8" t="n">
         <v>7.8</v>
@@ -2393,10 +2393,10 @@
         <v>1.54</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.14</v>
@@ -2438,7 +2438,7 @@
         <v>95</v>
       </c>
       <c r="Y8" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="Z8" t="n">
         <v>21</v>
@@ -2447,13 +2447,13 @@
         <v>21</v>
       </c>
       <c r="AB8" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AC8" t="n">
         <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>15.5</v>
@@ -2462,7 +2462,7 @@
         <v>85</v>
       </c>
       <c r="AG8" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AH8" t="n">
         <v>19</v>
@@ -2474,13 +2474,13 @@
         <v>180</v>
       </c>
       <c r="AK8" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN8" t="n">
         <v>27</v>
@@ -2489,55 +2489,55 @@
         <v>3.35</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG8" t="n">
         <v>2.88</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -2635,28 +2635,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G9" t="n">
         <v>1.71</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
         <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
         <v>5.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
         <v>9.4</v>
@@ -2665,7 +2665,7 @@
         <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
         <v>1.31</v>
@@ -2677,7 +2677,7 @@
         <v>1.76</v>
       </c>
       <c r="T9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U9" t="n">
         <v>3.15</v>
@@ -2686,19 +2686,19 @@
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X9" t="n">
         <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
         <v>55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB9" t="n">
         <v>22</v>
@@ -2707,7 +2707,7 @@
         <v>14.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>46</v>
@@ -2731,13 +2731,13 @@
         <v>15.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM9" t="n">
         <v>44</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO9" t="n">
         <v>23</v>
@@ -2749,7 +2749,7 @@
         <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS9" t="n">
         <v>60</v>
@@ -2767,7 +2767,7 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
@@ -2776,7 +2776,7 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
         <v>17.5</v>
@@ -2785,7 +2785,7 @@
         <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BE9" t="n">
         <v>24</v>
@@ -2812,7 +2812,7 @@
         <v>55</v>
       </c>
       <c r="BM9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN9" t="n">
         <v>5.6</v>
@@ -2824,10 +2824,10 @@
         <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS9" t="n">
         <v>6</v>
@@ -2842,23 +2842,23 @@
         <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I10" t="n">
         <v>1.79</v>
@@ -2907,7 +2907,7 @@
         <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
@@ -2952,7 +2952,7 @@
         <v>13.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB10" t="n">
         <v>24</v>
@@ -2964,31 +2964,31 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF10" t="n">
         <v>42</v>
       </c>
       <c r="AG10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
         <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="n">
         <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>42</v>
@@ -3033,13 +3033,13 @@
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BD10" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
         <v>55</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.37</v>
@@ -3167,13 +3167,13 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
         <v>2.1</v>
@@ -3191,46 +3191,46 @@
         <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
         <v>24</v>
@@ -3242,46 +3242,46 @@
         <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
         <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW11" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
         <v>55</v>
@@ -3296,7 +3296,7 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BF11" t="n">
         <v>15</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>2.98</v>
@@ -3421,7 +3421,7 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.5</v>
@@ -3448,7 +3448,7 @@
         <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
         <v>11</v>
@@ -3457,7 +3457,7 @@
         <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
         <v>60</v>
@@ -3469,7 +3469,7 @@
         <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
         <v>48</v>
@@ -3478,25 +3478,25 @@
         <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AJ12" t="n">
-        <v>75</v>
+        <v>340</v>
       </c>
       <c r="AK12" t="n">
         <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM12" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
         <v>65</v>
@@ -3514,7 +3514,7 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT12" t="n">
         <v>8</v>
@@ -3526,7 +3526,7 @@
         <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
         <v>14.5</v>
@@ -3538,22 +3538,22 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG12" t="n">
         <v>32</v>
@@ -3562,7 +3562,7 @@
         <v>2.82</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>3.9</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
         <v>1.99</v>
@@ -3702,7 +3702,7 @@
         <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -3714,7 +3714,7 @@
         <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB13" t="n">
         <v>15</v>
@@ -3726,7 +3726,7 @@
         <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF13" t="n">
         <v>34</v>
@@ -3735,7 +3735,7 @@
         <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
         <v>60</v>
@@ -3747,10 +3747,10 @@
         <v>70</v>
       </c>
       <c r="AL13" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM13" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
         <v>85</v>
@@ -3795,19 +3795,19 @@
         <v>28</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>48</v>
+        <v>5.8</v>
       </c>
       <c r="BG13" t="n">
         <v>15</v>
@@ -3822,13 +3822,13 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN13" t="n">
         <v>7.8</v>
@@ -3840,13 +3840,13 @@
         <v>40</v>
       </c>
       <c r="BQ13" t="n">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
         <v>4.9</v>
@@ -3858,23 +3858,23 @@
         <v>17</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BX13" t="n">
         <v>36</v>
       </c>
       <c r="BY13" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BZ13" t="n">
         <v>36</v>
       </c>
       <c r="CA13" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -3974,43 +3974,43 @@
         <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AF14" t="n">
         <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AK14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="AM14" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AP14" t="n">
         <v>7.8</v>
@@ -4019,52 +4019,52 @@
         <v>7.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH14" t="n">
         <v>2.9</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>America RN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Betim Futebol</t>
+          <t>Trem AP</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4404,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>America RN</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trem AP</t>
+          <t>Betim Futebol</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4440,19 +4440,19 @@
         <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="P16" t="n">
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H17" t="n">
         <v>4.7</v>
@@ -4691,7 +4691,7 @@
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
         <v>1.48</v>
@@ -4709,16 +4709,16 @@
         <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>12</v>
@@ -4745,10 +4745,10 @@
         <v>95</v>
       </c>
       <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
         <v>12</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>13</v>
       </c>
       <c r="AH17" t="n">
         <v>25</v>
@@ -4760,7 +4760,7 @@
         <v>24</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
         <v>65</v>
@@ -4781,10 +4781,10 @@
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
         <v>6</v>
@@ -4796,7 +4796,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
@@ -4805,10 +4805,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
         <v>19.5</v>
@@ -4817,16 +4817,16 @@
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH17" t="n">
         <v>2.92</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
         <v>1.31</v>
@@ -5053,7 +5053,7 @@
         <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,34 +857,34 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>1.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
         <v>1.7</v>
@@ -893,10 +893,10 @@
         <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,16 +905,16 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="X2" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -941,7 +941,7 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -956,64 +956,64 @@
         <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="BG2" t="n">
         <v>1.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J3" t="n">
         <v>7.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.25</v>
@@ -1135,34 +1135,34 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
@@ -1180,7 +1180,7 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD3" t="n">
         <v>48</v>
@@ -1192,7 +1192,7 @@
         <v>8.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>34</v>
@@ -1204,7 +1204,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL3" t="n">
         <v>36</v>
@@ -1213,10 +1213,10 @@
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AO3" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
@@ -1243,7 +1243,7 @@
         <v>46</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB3" t="n">
         <v>8.800000000000001</v>
@@ -1261,7 +1261,7 @@
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
         <v>70</v>
@@ -1270,7 +1270,7 @@
         <v>3.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH3" t="n">
         <v>5</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4</v>
@@ -1312,7 +1312,7 @@
         <v>16.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1327,14 +1327,14 @@
         <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CA3" t="n">
         <v>5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>2.54</v>
       </c>
       <c r="J4" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
         <v>1.55</v>
       </c>
       <c r="M4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.13</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.12</v>
       </c>
       <c r="S4" t="n">
         <v>6.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
         <v>42</v>
       </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>110</v>
-      </c>
       <c r="AF4" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AG4" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>3.95</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.33</v>
+        <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.31</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.21</v>
+        <v>3.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.33</v>
+        <v>4.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.31</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.29</v>
+        <v>5.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.32</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.32</v>
+        <v>6.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="n">
         <v>3.4</v>
@@ -1628,22 +1628,22 @@
         <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K5" t="n">
         <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.63</v>
@@ -1655,52 +1655,52 @@
         <v>2.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
         <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X5" t="n">
         <v>7.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
         <v>320</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
         <v>75</v>
@@ -1709,13 +1709,13 @@
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="AK5" t="n">
         <v>290</v>
       </c>
       <c r="AL5" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
@@ -1724,10 +1724,10 @@
         <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.6</v>
@@ -1736,7 +1736,7 @@
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>6.8</v>
@@ -1748,7 +1748,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1760,89 +1760,89 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BI5" t="n">
         <v>2.06</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
         <v>4.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="BT5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU5" t="n">
         <v>4.3</v>
       </c>
       <c r="BV5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -1885,13 +1885,13 @@
         <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
@@ -2044,13 +2044,13 @@
         <v>13.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BN6" t="n">
         <v>4.9</v>
@@ -2062,41 +2062,41 @@
         <v>19.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR6" t="n">
         <v>48</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
         <v>60</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>85</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>55</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I7" t="n">
         <v>8.6</v>
@@ -2145,40 +2145,40 @@
         <v>7.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P7" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S7" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="T7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U7" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="X7" t="n">
         <v>70</v>
@@ -2205,7 +2205,7 @@
         <v>210</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2217,7 +2217,7 @@
         <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
@@ -2229,73 +2229,73 @@
         <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB7" t="n">
+      <c r="BF7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
         <v>4.6</v>
@@ -2304,53 +2304,53 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BT7" t="n">
         <v>13</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
         <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
         <v>13</v>
@@ -2537,7 +2537,7 @@
         <v>7.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
         <v>2.88</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>1.65</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H9" t="n">
         <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
         <v>5.3</v>
@@ -2680,13 +2680,13 @@
         <v>1.4</v>
       </c>
       <c r="U9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V9" t="n">
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X9" t="n">
         <v>55</v>
@@ -2722,7 +2722,7 @@
         <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
         <v>22</v>
@@ -2737,7 +2737,7 @@
         <v>44</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO9" t="n">
         <v>23</v>
@@ -2749,7 +2749,7 @@
         <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS9" t="n">
         <v>60</v>
@@ -2794,7 +2794,7 @@
         <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH9" t="n">
         <v>6.4</v>
@@ -2818,7 +2818,7 @@
         <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G10" t="n">
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K10" t="n">
         <v>4.7</v>
@@ -2913,7 +2913,7 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -2937,10 +2937,10 @@
         <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
@@ -2988,7 +2988,7 @@
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AN10" t="n">
         <v>42</v>
@@ -3006,7 +3006,7 @@
         <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT10" t="n">
         <v>21</v>
@@ -3015,7 +3015,7 @@
         <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
         <v>14</v>
@@ -3033,13 +3033,13 @@
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD10" t="n">
         <v>42</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>20</v>
       </c>
       <c r="BE10" t="n">
         <v>55</v>
@@ -3090,7 +3090,7 @@
         <v>4.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV10" t="n">
         <v>11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -3155,19 +3155,19 @@
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.37</v>
@@ -3176,7 +3176,7 @@
         <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
@@ -3191,10 +3191,10 @@
         <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
         <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
         <v>24</v>
@@ -3242,10 +3242,10 @@
         <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO11" t="n">
         <v>80</v>
@@ -3257,10 +3257,10 @@
         <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
@@ -3272,7 +3272,7 @@
         <v>17</v>
       </c>
       <c r="AW11" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AX11" t="n">
         <v>10</v>
@@ -3287,7 +3287,7 @@
         <v>55</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
@@ -3296,10 +3296,10 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BG11" t="n">
         <v>50</v>
@@ -3308,19 +3308,19 @@
         <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN11" t="n">
         <v>4.6</v>
@@ -3332,28 +3332,28 @@
         <v>15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR11" t="n">
         <v>32</v>
       </c>
       <c r="BS11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>7.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW11" t="n">
         <v>11.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY11" t="n">
         <v>12.5</v>
@@ -3362,11 +3362,11 @@
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>3.35</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I12" t="n">
         <v>2.9</v>
@@ -3412,37 +3412,37 @@
         <v>2.98</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
         <v>1.52</v>
@@ -3478,7 +3478,7 @@
         <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AH12" t="n">
         <v>60</v>
@@ -3487,19 +3487,19 @@
         <v>380</v>
       </c>
       <c r="AJ12" t="n">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="AK12" t="n">
         <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>170</v>
+        <v>380</v>
       </c>
       <c r="AM12" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AO12" t="n">
         <v>50</v>
@@ -3514,7 +3514,7 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
         <v>8</v>
@@ -3538,19 +3538,19 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE12" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6</v>
       </c>
       <c r="BF12" t="n">
         <v>9.4</v>
@@ -3559,7 +3559,7 @@
         <v>32</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI12" t="n">
         <v>2.54</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN12" t="n">
         <v>6.2</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT12" t="n">
         <v>5.6</v>
@@ -3604,7 +3604,7 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
@@ -3616,11 +3616,11 @@
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
         <v>1.46</v>
@@ -3717,7 +3717,7 @@
         <v>28</v>
       </c>
       <c r="AB13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
@@ -3762,55 +3762,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>19</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>5.3</v>
       </c>
       <c r="AY13" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>28</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC13" t="n">
         <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
         <v>5.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BH13" t="n">
         <v>3.15</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -3905,100 +3905,100 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.8</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>3.25</v>
       </c>
-      <c r="H14" t="n">
-        <v>2.7</v>
-      </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K14" t="n">
         <v>3.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O14" t="n">
         <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
         <v>4.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="X14" t="n">
         <v>9.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC14" t="n">
         <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="AL14" t="n">
         <v>380</v>
@@ -4010,73 +4010,73 @@
         <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4085,16 +4085,16 @@
         <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4103,22 +4103,22 @@
         <v>8.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>1.22</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M15" t="n">
         <v>1.02</v>
       </c>
-      <c r="K15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N15" t="n">
-        <v>1.27</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>1.27</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
-        <v>1.19</v>
+        <v>2.32</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -4413,230 +4413,230 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.57</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.39</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>4.7</v>
@@ -4685,13 +4685,13 @@
         <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
         <v>1.48</v>
@@ -4733,7 +4733,7 @@
         <v>150</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC17" t="n">
         <v>8</v>
@@ -4757,7 +4757,7 @@
         <v>120</v>
       </c>
       <c r="AJ17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK17" t="n">
         <v>27</v>
@@ -4781,25 +4781,25 @@
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT17" t="n">
         <v>6</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY17" t="n">
         <v>9.199999999999999</v>
@@ -4808,7 +4808,7 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB17" t="n">
         <v>19.5</v>
@@ -4817,16 +4817,16 @@
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH17" t="n">
         <v>2.92</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -4921,40 +4921,40 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
         <v>3.35</v>
       </c>
       <c r="L18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
         <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O18" t="n">
         <v>1.47</v>
       </c>
       <c r="P18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
         <v>1.22</v>
@@ -4963,16 +4963,16 @@
         <v>4.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="X18" t="n">
         <v>11.5</v>
@@ -4984,10 +4984,10 @@
         <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC18" t="n">
         <v>7.6</v>
@@ -4996,13 +4996,13 @@
         <v>20</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AF18" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
         <v>26</v>
@@ -5011,10 +5011,10 @@
         <v>90</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
         <v>65</v>
@@ -5023,67 +5023,67 @@
         <v>190</v>
       </c>
       <c r="AN18" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
         <v>19</v>
       </c>
       <c r="AS18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB18" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA18" t="n">
+      <c r="BC18" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF18" t="n">
         <v>21</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BI18" t="n">
         <v>2.32</v>
@@ -5098,53 +5098,53 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS18" t="n">
         <v>8.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -881,13 +881,13 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.92</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
         <v>1.74</v>
@@ -896,7 +896,7 @@
         <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
@@ -917,22 +917,22 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>95</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
@@ -944,7 +944,7 @@
         <v>160</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ2" t="n">
         <v>970</v>
@@ -962,58 +962,58 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.22</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG2" t="n">
         <v>1.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
         <v>7.2</v>
@@ -1129,13 +1129,13 @@
         <v>7.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1147,7 +1147,7 @@
         <v>1.49</v>
       </c>
       <c r="R3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
         <v>2.26</v>
@@ -1156,7 +1156,7 @@
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
@@ -1180,7 +1180,7 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
         <v>48</v>
@@ -1198,7 +1198,7 @@
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
         <v>9.800000000000001</v>
@@ -1219,16 +1219,16 @@
         <v>220</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AR3" t="n">
         <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
         <v>46</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
         <v>25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -1380,31 +1380,31 @@
         <v>2.72</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="R4" t="n">
         <v>1.13</v>
       </c>
       <c r="S4" t="n">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
         <v>2.28</v>
@@ -1425,7 +1425,7 @@
         <v>6.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA4" t="n">
         <v>38</v>
@@ -1449,7 +1449,7 @@
         <v>21</v>
       </c>
       <c r="AH4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1467,64 +1467,64 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
         <v>48</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB4" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE4" t="n">
         <v>7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
         <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
         <v>2.56</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.9</v>
+        <v>2.04</v>
       </c>
       <c r="BN4" t="n">
         <v>7.6</v>
@@ -1554,13 +1554,13 @@
         <v>50</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>1.97</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="BT4" t="n">
         <v>5.1</v>
@@ -1572,23 +1572,23 @@
         <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.8</v>
+        <v>1.89</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.4</v>
+        <v>1.98</v>
       </c>
       <c r="BZ4" t="n">
         <v>70</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="I5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L5" t="n">
         <v>1.54</v>
@@ -1667,37 +1667,37 @@
         <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
         <v>7.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA5" t="n">
         <v>320</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>290</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>16.5</v>
@@ -1730,55 +1730,55 @@
         <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
         <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
         <v>6.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB5" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7</v>
       </c>
       <c r="BC5" t="n">
         <v>7</v>
       </c>
       <c r="BD5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG5" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7</v>
       </c>
       <c r="BH5" t="n">
         <v>2.58</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G7" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
         <v>1.18</v>
@@ -2151,16 +2151,16 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P7" t="n">
         <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
         <v>2.02</v>
@@ -2169,13 +2169,13 @@
         <v>1.74</v>
       </c>
       <c r="T7" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
         <v>2.92</v>
@@ -2187,16 +2187,16 @@
         <v>150</v>
       </c>
       <c r="Z7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AC7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>85</v>
@@ -2205,88 +2205,88 @@
         <v>210</v>
       </c>
       <c r="AF7" t="n">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AI7" t="n">
         <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>16.5</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.85</v>
+        <v>29</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.5</v>
+        <v>1.31</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>1.34</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>1.29</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>1.34</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>1.33</v>
       </c>
       <c r="AX7" t="n">
-        <v>11.5</v>
+        <v>1.33</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>1.33</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>1.31</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>1.33</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>1.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="n">
         <v>6.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G9" t="n">
         <v>1.7</v>
@@ -2647,7 +2647,7 @@
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
         <v>5.3</v>
@@ -2686,7 +2686,7 @@
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X9" t="n">
         <v>55</v>
@@ -2719,7 +2719,7 @@
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI9" t="n">
         <v>38</v>
@@ -2731,7 +2731,7 @@
         <v>15.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>44</v>
@@ -2740,7 +2740,7 @@
         <v>4.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
         <v>28</v>
@@ -2776,22 +2776,22 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BE9" t="n">
         <v>24</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
         <v>19.5</v>
@@ -2806,7 +2806,7 @@
         <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL9" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP9" t="n">
         <v>10.5</v>
@@ -2836,7 +2836,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
         <v>32</v>
@@ -2851,14 +2851,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CA9" t="n">
         <v>4.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I10" t="n">
         <v>1.75</v>
@@ -2913,19 +2913,19 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q10" t="n">
         <v>1.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
         <v>2.4</v>
@@ -2952,7 +2952,7 @@
         <v>13.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="n">
         <v>24</v>
@@ -2994,7 +2994,7 @@
         <v>42</v>
       </c>
       <c r="AO10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP10" t="n">
         <v>19.5</v>
@@ -3006,7 +3006,7 @@
         <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>21</v>
@@ -3033,7 +3033,7 @@
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC10" t="n">
         <v>44</v>
@@ -3090,7 +3090,7 @@
         <v>4.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BV10" t="n">
         <v>11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -3158,7 +3158,7 @@
         <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.44</v>
@@ -3167,34 +3167,34 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
         <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
         <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ11" t="n">
         <v>24</v>
@@ -3242,28 +3242,28 @@
         <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
         <v>29</v>
       </c>
       <c r="AS11" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
@@ -3296,7 +3296,7 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="BF11" t="n">
         <v>17.5</v>
@@ -3305,49 +3305,49 @@
         <v>50</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="BJ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BR11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU11" t="n">
         <v>6.4</v>
       </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BV11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BW11" t="n">
         <v>11.5</v>
@@ -3356,17 +3356,17 @@
         <v>65</v>
       </c>
       <c r="BY11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -3400,169 +3400,169 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N12" t="n">
         <v>2.64</v>
       </c>
-      <c r="I12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.66</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P12" t="n">
         <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD12" t="n">
         <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI12" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AK12" t="n">
         <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="AN12" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO12" t="n">
         <v>50</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="AT12" t="n">
         <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY12" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.3</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.2</v>
+        <v>26</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.3</v>
+        <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.6</v>
+        <v>48</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BG12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN12" t="n">
         <v>6.2</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT12" t="n">
         <v>5.6</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.46</v>
@@ -3705,7 +3705,7 @@
         <v>1.27</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
         <v>8.4</v>
@@ -3759,7 +3759,7 @@
         <v>22</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.8</v>
@@ -3768,7 +3768,7 @@
         <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.1</v>
+        <v>16.5</v>
       </c>
       <c r="AT13" t="n">
         <v>11</v>
@@ -3783,7 +3783,7 @@
         <v>21</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>14.5</v>
@@ -3792,22 +3792,22 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.7</v>
+        <v>28</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
         <v>17.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H14" t="n">
         <v>3.25</v>
@@ -3965,7 +3965,7 @@
         <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3983,7 +3983,7 @@
         <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG14" t="n">
         <v>13</v>
@@ -4022,7 +4022,7 @@
         <v>17.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>6.8</v>
@@ -4106,7 +4106,7 @@
         <v>6.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV14" t="n">
         <v>32</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
         <v>2.32</v>
       </c>
       <c r="T15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U15" t="n">
         <v>1.52</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="G16" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="H16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.45</v>
@@ -4446,142 +4446,142 @@
         <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
         <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
         <v>95</v>
       </c>
       <c r="AA16" t="n">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
         <v>42</v>
       </c>
       <c r="AE16" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI16" t="n">
         <v>220</v>
       </c>
-      <c r="AF16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>200</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="AN16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO16" t="n">
-        <v>390</v>
+        <v>460</v>
       </c>
       <c r="AP16" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BD16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF16" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BG16" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK16" t="n">
         <v>6.2</v>
@@ -4590,28 +4590,28 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.5</v>
+        <v>1.51</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BP16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BR16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
         <v>2.36</v>
       </c>
       <c r="BT16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU16" t="n">
         <v>6</v>
@@ -4620,7 +4620,7 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4629,14 +4629,14 @@
         <v>2.48</v>
       </c>
       <c r="BZ16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
         <v>2.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.94</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H17" t="n">
         <v>4.7</v>
@@ -4679,10 +4679,10 @@
         <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.54</v>
@@ -4691,7 +4691,7 @@
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
         <v>1.48</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
         <v>2.26</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
         <v>3.05</v>
@@ -5011,7 +5011,7 @@
         <v>90</v>
       </c>
       <c r="AJ18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
         <v>34</v>
@@ -5056,7 +5056,7 @@
         <v>9.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>18.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
         <v>1.67</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -881,22 +881,22 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
         <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,7 +905,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
         <v>2.48</v>
@@ -926,7 +926,7 @@
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AD2" t="n">
         <v>500</v>
@@ -941,7 +941,7 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AI2" t="n">
         <v>700</v>
@@ -965,28 +965,28 @@
         <v>700</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
         <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
         <v>4.7</v>
@@ -995,28 +995,28 @@
         <v>4.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
         <v>1.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BD2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.34</v>
       </c>
-      <c r="BE2" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
         <v>1.26</v>
       </c>
       <c r="G3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H3" t="n">
         <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J3" t="n">
         <v>7.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1144,25 +1144,25 @@
         <v>2.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
         <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
@@ -1171,10 +1171,10 @@
         <v>60</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA3" t="n">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="AB3" t="n">
         <v>11.5</v>
@@ -1210,10 +1210,10 @@
         <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AO3" t="n">
         <v>220</v>
@@ -1258,10 +1258,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
         <v>70</v>
@@ -1270,7 +1270,7 @@
         <v>3.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -1365,91 +1365,91 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.5</v>
       </c>
-      <c r="G4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>8.4</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.8</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1470,125 +1470,125 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>1.34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="AX4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BD4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>70</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>2</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
         <v>2.66</v>
@@ -1637,13 +1637,13 @@
         <v>3.05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
         <v>1.63</v>
@@ -1658,25 +1658,25 @@
         <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
         <v>7.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="Z5" t="n">
         <v>17.5</v>
@@ -1700,16 +1700,16 @@
         <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="AK5" t="n">
         <v>290</v>
@@ -1727,122 +1727,122 @@
         <v>500</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX5" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI5" t="n">
         <v>2.06</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>1.96</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.8</v>
+        <v>1.93</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
         <v>1.16</v>
@@ -1915,25 +1915,25 @@
         <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
@@ -1942,16 +1942,16 @@
         <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>260</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1963,10 +1963,10 @@
         <v>540</v>
       </c>
       <c r="AJ6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>75</v>
@@ -1975,7 +1975,7 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
@@ -1984,119 +1984,119 @@
         <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA6" t="n">
         <v>5.6</v>
       </c>
-      <c r="AX6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN6" t="n">
         <v>4.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BP6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR6" t="n">
         <v>48</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BX6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BZ6" t="n">
         <v>55</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -2127,76 +2127,76 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P7" t="n">
         <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="X7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Y7" t="n">
         <v>150</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB7" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD7" t="n">
         <v>85</v>
@@ -2205,100 +2205,100 @@
         <v>210</v>
       </c>
       <c r="AF7" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>15.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="n">
-        <v>29</v>
+        <v>3.95</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.33</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.34</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.29</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.34</v>
+        <v>5</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.32</v>
+        <v>5.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.33</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.27</v>
+        <v>4.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.33</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.28</v>
+        <v>4.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.33</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.34</v>
+        <v>6.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>5.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="BP7" t="n">
         <v>8.6</v>
@@ -2319,16 +2319,16 @@
         <v>4.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BS7" t="n">
         <v>5.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2343,14 +2343,14 @@
         <v>6.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G8" t="n">
         <v>7.8</v>
@@ -2390,10 +2390,10 @@
         <v>1.43</v>
       </c>
       <c r="I8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
         <v>6.8</v>
@@ -2429,7 +2429,7 @@
         <v>3.1</v>
       </c>
       <c r="V8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="W8" t="n">
         <v>1.15</v>
@@ -2471,7 +2471,7 @@
         <v>21</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AK8" t="n">
         <v>130</v>
@@ -2489,46 +2489,46 @@
         <v>3.35</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8" t="n">
         <v>7.6</v>
@@ -2537,7 +2537,7 @@
         <v>7.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG8" t="n">
         <v>2.88</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2638,22 @@
         <v>1.68</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2662,43 +2662,43 @@
         <v>9.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="T9" t="n">
         <v>1.4</v>
       </c>
       <c r="U9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V9" t="n">
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X9" t="n">
         <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
         <v>55</v>
       </c>
       <c r="AA9" t="n">
-        <v>690</v>
+        <v>300</v>
       </c>
       <c r="AB9" t="n">
         <v>22</v>
@@ -2710,10 +2710,10 @@
         <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
@@ -2725,7 +2725,7 @@
         <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
         <v>15.5</v>
@@ -2734,37 +2734,37 @@
         <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO9" t="n">
         <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ9" t="n">
         <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AS9" t="n">
         <v>60</v>
       </c>
       <c r="AT9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
         <v>15.5</v>
@@ -2773,31 +2773,31 @@
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BC9" t="n">
         <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BE9" t="n">
         <v>24</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI9" t="n">
         <v>5.2</v>
@@ -2806,16 +2806,16 @@
         <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL9" t="n">
         <v>55</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO9" t="n">
         <v>4.3</v>
@@ -2824,41 +2824,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BR9" t="n">
         <v>16.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BT9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX9" t="n">
         <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>9</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="I10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="J10" t="n">
         <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V10" t="n">
         <v>2.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
         <v>13.5</v>
@@ -2955,7 +2955,7 @@
         <v>20</v>
       </c>
       <c r="AB10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC10" t="n">
         <v>11</v>
@@ -2976,10 +2976,10 @@
         <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK10" t="n">
         <v>55</v>
@@ -2988,10 +2988,10 @@
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="AN10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO10" t="n">
         <v>7.2</v>
@@ -3033,10 +3033,10 @@
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="BD10" t="n">
         <v>42</v>
@@ -3045,7 +3045,7 @@
         <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
         <v>6.4</v>
@@ -3054,7 +3054,7 @@
         <v>4.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.199999999999999</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
         <v>2.04</v>
@@ -3152,7 +3152,7 @@
         <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
         <v>3.45</v>
@@ -3161,31 +3161,31 @@
         <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
         <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
         <v>1.96</v>
@@ -3230,7 +3230,7 @@
         <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
         <v>24</v>
@@ -3242,22 +3242,22 @@
         <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>19.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS11" t="n">
         <v>85</v>
@@ -3266,7 +3266,7 @@
         <v>7.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
         <v>17</v>
@@ -3278,13 +3278,13 @@
         <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -3302,7 +3302,7 @@
         <v>17.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>50</v>
+        <v>13.5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.5</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN11" t="n">
         <v>4.5</v>
@@ -3332,7 +3332,7 @@
         <v>14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BR11" t="n">
         <v>30</v>
@@ -3356,17 +3356,17 @@
         <v>65</v>
       </c>
       <c r="BY11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>28</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -3397,64 +3397,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I12" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M12" t="n">
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O12" t="n">
         <v>1.56</v>
       </c>
       <c r="P12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
         <v>17.5</v>
@@ -3472,7 +3472,7 @@
         <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -3481,7 +3481,7 @@
         <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI12" t="n">
         <v>120</v>
@@ -3502,19 +3502,19 @@
         <v>140</v>
       </c>
       <c r="AO12" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR12" t="n">
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
         <v>8</v>
@@ -3535,7 +3535,7 @@
         <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>34</v>
@@ -3544,13 +3544,13 @@
         <v>28</v>
       </c>
       <c r="BC12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BD12" t="n">
         <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF12" t="n">
         <v>29</v>
@@ -3559,10 +3559,10 @@
         <v>34</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3574,10 +3574,10 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO12" t="n">
         <v>5.2</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT12" t="n">
         <v>5.6</v>
@@ -3601,26 +3601,26 @@
         <v>4.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
         <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -3657,49 +3657,49 @@
         <v>4.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
         <v>1.87</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W13" t="n">
         <v>1.27</v>
@@ -3759,40 +3759,40 @@
         <v>22</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>6.2</v>
@@ -3810,7 +3810,7 @@
         <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH13" t="n">
         <v>3.15</v>
@@ -3822,28 +3822,28 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN13" t="n">
         <v>7.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS13" t="n">
         <v>8.6</v>
@@ -3852,29 +3852,29 @@
         <v>4.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV13" t="n">
         <v>17</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX13" t="n">
         <v>36</v>
       </c>
       <c r="BY13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>36</v>
       </c>
       <c r="CA13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -3905,40 +3905,40 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P14" t="n">
         <v>1.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
@@ -3947,19 +3947,19 @@
         <v>4.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
         <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y14" t="n">
         <v>11</v>
@@ -3968,16 +3968,16 @@
         <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
         <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
         <v>55</v>
@@ -4013,13 +4013,13 @@
         <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS14" t="n">
         <v>8.199999999999999</v>
@@ -4031,31 +4031,31 @@
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
         <v>32</v>
       </c>
       <c r="AX14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BC14" t="n">
         <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
         <v>8.800000000000001</v>
@@ -4082,53 +4082,53 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW14" t="n">
         <v>7.8</v>
       </c>
       <c r="BX14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -4165,19 +4165,19 @@
         <v>1.22</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I15" t="n">
         <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
@@ -4210,7 +4210,7 @@
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="X15" t="n">
         <v>30</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>1.39</v>
@@ -4629,14 +4629,14 @@
         <v>2.48</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA16" t="n">
         <v>2.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -4670,43 +4670,43 @@
         <v>1.94</v>
       </c>
       <c r="G17" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
         <v>1.48</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
         <v>2.16</v>
@@ -4715,118 +4715,118 @@
         <v>1.79</v>
       </c>
       <c r="V17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA17" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>95</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU17" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7</v>
-      </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="AX17" t="n">
         <v>9</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BB17" t="n">
         <v>19.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BH17" t="n">
         <v>2.92</v>
@@ -4856,13 +4856,13 @@
         <v>16</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT17" t="n">
         <v>8.199999999999999</v>
@@ -4871,7 +4871,7 @@
         <v>4.9</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW17" t="n">
         <v>9.800000000000001</v>
@@ -4886,11 +4886,11 @@
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -4921,79 +4921,79 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M18" t="n">
         <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
         <v>1.47</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
         <v>4.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X18" t="n">
         <v>11.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>90</v>
@@ -5005,10 +5005,10 @@
         <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ18" t="n">
         <v>34</v>
@@ -5017,10 +5017,10 @@
         <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="n">
         <v>32</v>
@@ -5029,61 +5029,61 @@
         <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>19</v>
+        <v>3.95</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF18" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>21</v>
-      </c>
       <c r="BG18" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI18" t="n">
         <v>2.32</v>
@@ -5092,7 +5092,7 @@
         <v>11.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5101,7 +5101,7 @@
         <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO18" t="n">
         <v>3.6</v>
@@ -5116,35 +5116,35 @@
         <v>40</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ18" t="n">
         <v>44</v>
       </c>
-      <c r="BW18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>42</v>
-      </c>
       <c r="CA18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,112 +857,112 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>530</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE2" t="n">
         <v>85</v>
       </c>
-      <c r="AD2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>700</v>
-      </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
         <v>13.5</v>
@@ -971,116 +971,116 @@
         <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.31</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.33</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.31</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.33</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.34</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.28</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1120,10 @@
         <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K3" t="n">
         <v>7.6</v>
@@ -1141,22 +1141,22 @@
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
@@ -1171,25 +1171,25 @@
         <v>60</v>
       </c>
       <c r="Z3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>680</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD3" t="n">
         <v>48</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1198,7 +1198,7 @@
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
         <v>9.800000000000001</v>
@@ -1213,37 +1213,37 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AO3" t="n">
         <v>220</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AQ3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AR3" t="n">
         <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV3" t="n">
         <v>38</v>
       </c>
       <c r="AW3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BB3" t="n">
         <v>8.800000000000001</v>
@@ -1264,77 +1264,77 @@
         <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BG3" t="n">
         <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BJ3" t="n">
         <v>13</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BR3" t="n">
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>16.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX3" t="n">
         <v>90</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>9</v>
       </c>
       <c r="CA3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1368,58 +1368,58 @@
         <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="J4" t="n">
         <v>2.42</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
         <v>1.45</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
         <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
         <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
@@ -1431,7 +1431,7 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>42</v>
@@ -1470,10 +1470,10 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.15</v>
@@ -1482,7 +1482,7 @@
         <v>4.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AT4" t="n">
         <v>3.55</v>
@@ -1494,37 +1494,37 @@
         <v>4.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="BA4" t="n">
         <v>5.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="BC4" t="n">
         <v>5.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
         <v>3.7</v>
@@ -1643,7 +1643,7 @@
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.63</v>
@@ -1652,22 +1652,22 @@
         <v>1.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R5" t="n">
         <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.37</v>
@@ -1682,7 +1682,7 @@
         <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>320</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>9</v>
@@ -1700,10 +1700,10 @@
         <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1721,67 +1721,67 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AR5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU5" t="n">
         <v>5.8</v>
       </c>
-      <c r="AS5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AV5" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BI5" t="n">
         <v>2.06</v>
@@ -1790,43 +1790,43 @@
         <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.96</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT5" t="n">
         <v>5.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.93</v>
+        <v>7.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
         <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
@@ -1897,52 +1897,52 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>25</v>
@@ -1951,10 +1951,10 @@
         <v>260</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>30</v>
@@ -1963,49 +1963,49 @@
         <v>540</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
@@ -2014,89 +2014,89 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BI6" t="n">
         <v>2.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
         <v>3.35</v>
       </c>
       <c r="BP6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.19</v>
@@ -2151,34 +2151,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="T7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="X7" t="n">
         <v>60</v>
@@ -2187,16 +2187,16 @@
         <v>150</v>
       </c>
       <c r="Z7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AD7" t="n">
         <v>85</v>
@@ -2205,13 +2205,13 @@
         <v>210</v>
       </c>
       <c r="AF7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>150</v>
@@ -2220,137 +2220,137 @@
         <v>15.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AW7" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BD7" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="n">
         <v>6.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BT7" t="n">
         <v>12.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="I8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K8" t="n">
         <v>6.8</v>
@@ -2405,34 +2405,34 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O8" t="n">
         <v>1.06</v>
       </c>
       <c r="P8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
         <v>1.21</v>
       </c>
       <c r="R8" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="S8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="U8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
         <v>95</v>
@@ -2441,7 +2441,7 @@
         <v>48</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
         <v>21</v>
@@ -2453,22 +2453,22 @@
         <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE8" t="n">
         <v>15.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AG8" t="n">
         <v>65</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ8" t="n">
         <v>170</v>
@@ -2480,67 +2480,67 @@
         <v>100</v>
       </c>
       <c r="AM8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>3.35</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AT8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BE8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BD8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.68</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.69</v>
-      </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.2</v>
@@ -2659,64 +2659,64 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y9" t="n">
         <v>44</v>
       </c>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="AB9" t="n">
         <v>22</v>
       </c>
       <c r="AC9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>15.5</v>
@@ -2728,73 +2728,73 @@
         <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL9" t="n">
         <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO9" t="n">
         <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AQ9" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AR9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AS9" t="n">
         <v>60</v>
       </c>
       <c r="AT9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AX9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BB9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BF9" t="n">
         <v>4.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="n">
         <v>6.2</v>
@@ -2803,7 +2803,7 @@
         <v>5.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
         <v>4.9</v>
@@ -2812,53 +2812,53 @@
         <v>55</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN9" t="n">
         <v>5.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR9" t="n">
         <v>16.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY9" t="n">
         <v>8</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>9</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G10" t="n">
         <v>5.1</v>
@@ -2898,16 +2898,16 @@
         <v>1.73</v>
       </c>
       <c r="I10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J10" t="n">
         <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
@@ -2916,22 +2916,22 @@
         <v>5.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
         <v>1.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
         <v>2.44</v>
@@ -2952,7 +2952,7 @@
         <v>13.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB10" t="n">
         <v>25</v>
@@ -2964,13 +2964,13 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF10" t="n">
         <v>42</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH10" t="n">
         <v>17.5</v>
@@ -2985,10 +2985,10 @@
         <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM10" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
         <v>40</v>
@@ -3015,7 +3015,7 @@
         <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW10" t="n">
         <v>14</v>
@@ -3033,10 +3033,10 @@
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
         <v>42</v>
@@ -3045,7 +3045,7 @@
         <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BG10" t="n">
         <v>6.4</v>
@@ -3060,7 +3060,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,7 +3072,7 @@
         <v>8.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BP10" t="n">
         <v>34</v>
@@ -3096,7 +3096,7 @@
         <v>11</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BX10" t="n">
         <v>21</v>
@@ -3108,11 +3108,11 @@
         <v>14.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
         <v>1.45</v>
@@ -3170,7 +3170,7 @@
         <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
         <v>1.79</v>
@@ -3179,7 +3179,7 @@
         <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
         <v>4.1</v>
@@ -3233,7 +3233,7 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK11" t="n">
         <v>23</v>
@@ -3245,7 +3245,7 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO11" t="n">
         <v>80</v>
@@ -3257,7 +3257,7 @@
         <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS11" t="n">
         <v>85</v>
@@ -3266,10 +3266,10 @@
         <v>7.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW11" t="n">
         <v>55</v>
@@ -3278,7 +3278,7 @@
         <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
         <v>17.5</v>
@@ -3305,7 +3305,7 @@
         <v>13.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI11" t="n">
         <v>3.05</v>
@@ -3314,19 +3314,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BN11" t="n">
         <v>4.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP11" t="n">
         <v>14</v>
@@ -3344,19 +3344,19 @@
         <v>7.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV11" t="n">
         <v>38</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>65</v>
       </c>
       <c r="BY11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
         <v>28</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="I12" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="n">
         <v>2.98</v>
@@ -3415,73 +3415,73 @@
         <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M12" t="n">
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O12" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P12" t="n">
         <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
         <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y12" t="n">
         <v>9.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9</v>
       </c>
       <c r="Z12" t="n">
         <v>17.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB12" t="n">
         <v>9.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
         <v>48</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
         <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI12" t="n">
         <v>120</v>
@@ -3502,37 +3502,37 @@
         <v>140</v>
       </c>
       <c r="AO12" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR12" t="n">
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX12" t="n">
         <v>17</v>
       </c>
       <c r="AY12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>20</v>
@@ -3541,7 +3541,7 @@
         <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC12" t="n">
         <v>29</v>
@@ -3553,7 +3553,7 @@
         <v>46</v>
       </c>
       <c r="BF12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BG12" t="n">
         <v>34</v>
@@ -3562,7 +3562,7 @@
         <v>2.72</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3574,10 +3574,10 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO12" t="n">
         <v>5.2</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT12" t="n">
         <v>5.6</v>
@@ -3604,23 +3604,23 @@
         <v>32</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX12" t="n">
         <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>3.9</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.47</v>
@@ -3693,7 +3693,7 @@
         <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.87</v>
@@ -3702,7 +3702,7 @@
         <v>1.83</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -3711,19 +3711,19 @@
         <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
         <v>28</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -3732,16 +3732,16 @@
         <v>34</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
         <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
         <v>70</v>
@@ -3753,13 +3753,13 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO13" t="n">
         <v>22</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AQ13" t="n">
         <v>5.8</v>
@@ -3786,52 +3786,52 @@
         <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AZ13" t="n">
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
         <v>14.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="BJ13" t="n">
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO13" t="n">
         <v>5.6</v>
@@ -3840,13 +3840,13 @@
         <v>42</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR13" t="n">
         <v>60</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>4.9</v>
@@ -3855,26 +3855,26 @@
         <v>3.6</v>
       </c>
       <c r="BV13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX13" t="n">
         <v>36</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>36</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -3905,103 +3905,103 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J14" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.72</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.56</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.58</v>
-      </c>
       <c r="X14" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="AA14" t="n">
         <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="AK14" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
@@ -4013,122 +4013,122 @@
         <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>38</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BN14" t="n">
         <v>5.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BR14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -4162,43 +4162,43 @@
         <v>1.17</v>
       </c>
       <c r="G15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H15" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
         <v>7.4</v>
       </c>
       <c r="K15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
         <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="T15" t="n">
         <v>2.54</v>
@@ -4210,34 +4210,34 @@
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="X15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Z15" t="n">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AG15" t="n">
         <v>14</v>
@@ -4246,143 +4246,143 @@
         <v>60</v>
       </c>
       <c r="AI15" t="n">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -4413,175 +4413,175 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="G16" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I16" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="O16" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
         <v>2.14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.62</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="BC16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>13.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>480</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>220</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>460</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>14</v>
       </c>
       <c r="BK16" t="n">
         <v>6.2</v>
@@ -4590,28 +4590,28 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.51</v>
+        <v>2.46</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BP16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BT16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU16" t="n">
         <v>6</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BZ16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
@@ -4694,13 +4694,13 @@
         <v>2.92</v>
       </c>
       <c r="O17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
@@ -4709,10 +4709,10 @@
         <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
         <v>1.23</v>
@@ -4730,7 +4730,7 @@
         <v>36</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
         <v>7</v>
@@ -4754,7 +4754,7 @@
         <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
         <v>22</v>
@@ -4772,16 +4772,16 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
         <v>13</v>
@@ -4799,7 +4799,7 @@
         <v>12.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
         <v>9.800000000000001</v>
@@ -4829,7 +4829,7 @@
         <v>13</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI17" t="n">
         <v>2.36</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN17" t="n">
         <v>4.6</v>
@@ -4856,13 +4856,13 @@
         <v>16</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT17" t="n">
         <v>8.199999999999999</v>
@@ -4874,7 +4874,7 @@
         <v>55</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -4924,67 +4924,67 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M18" t="n">
         <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="O18" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="X18" t="n">
         <v>11.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
         <v>8.4</v>
@@ -4993,76 +4993,76 @@
         <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
         <v>110</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK18" t="n">
         <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ18" t="n">
         <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV18" t="n">
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -5071,16 +5071,16 @@
         <v>20</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF18" t="n">
         <v>18.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH18" t="n">
         <v>2.92</v>
@@ -5089,7 +5089,7 @@
         <v>2.32</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK18" t="n">
         <v>5.7</v>
@@ -5101,13 +5101,13 @@
         <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ18" t="n">
         <v>6.8</v>
@@ -5116,35 +5116,35 @@
         <v>40</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW18" t="n">
         <v>9</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
         <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>11.5</v>
+        <v>75</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="BB2" t="n">
         <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP2" t="n">
         <v>11</v>
       </c>
-      <c r="BK2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
         <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="BX2" t="n">
         <v>65</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1111,85 +1111,85 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G3" t="n">
         <v>1.26</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="H3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
         <v>7.4</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R3" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>680</v>
+        <v>560</v>
       </c>
       <c r="AB3" t="n">
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AE3" t="n">
         <v>200</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1198,22 +1198,22 @@
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AO3" t="n">
         <v>220</v>
@@ -1222,28 +1222,28 @@
         <v>30</v>
       </c>
       <c r="AQ3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AR3" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AS3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>14.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AW3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1252,28 +1252,28 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE3" t="n">
         <v>80</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BG3" t="n">
         <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI3" t="n">
         <v>4.4</v>
@@ -1288,10 +1288,10 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO3" t="n">
         <v>3.55</v>
@@ -1303,38 +1303,38 @@
         <v>5.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>16.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="I4" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>2.42</v>
@@ -1383,7 +1383,7 @@
         <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
@@ -1398,7 +1398,7 @@
         <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R4" t="n">
         <v>1.13</v>
@@ -1413,13 +1413,13 @@
         <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
@@ -1476,55 +1476,55 @@
         <v>1.44</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.15</v>
+        <v>1.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>1.37</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.1</v>
+        <v>1.41</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>1.44</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.8</v>
+        <v>1.44</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
         <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>1.66</v>
@@ -1643,19 +1643,19 @@
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.63</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
         <v>6.4</v>
@@ -1667,7 +1667,7 @@
         <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
         <v>1.37</v>
@@ -1682,7 +1682,7 @@
         <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>320</v>
       </c>
       <c r="AB5" t="n">
         <v>9</v>
@@ -1721,7 +1721,7 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
@@ -1733,10 +1733,10 @@
         <v>6.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1748,28 +1748,28 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="AY5" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
         <v>9</v>
@@ -1778,10 +1778,10 @@
         <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI5" t="n">
         <v>2.06</v>
@@ -1790,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,47 +1802,47 @@
         <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>5.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.58</v>
@@ -1912,19 +1912,19 @@
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
         <v>9.199999999999999</v>
@@ -1933,13 +1933,13 @@
         <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
@@ -1951,7 +1951,7 @@
         <v>260</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
@@ -1969,16 +1969,16 @@
         <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="AP6" t="n">
         <v>7</v>
@@ -2002,7 +2002,7 @@
         <v>17</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -2014,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
         <v>18.5</v>
@@ -2026,31 +2026,31 @@
         <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
         <v>19.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
@@ -2062,41 +2062,41 @@
         <v>17.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU6" t="n">
         <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>7</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>7.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>50</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G7" t="n">
         <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J7" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K7" t="n">
         <v>6.8</v>
@@ -2157,7 +2157,7 @@
         <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q7" t="n">
         <v>1.33</v>
@@ -2172,7 +2172,7 @@
         <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -2205,7 +2205,7 @@
         <v>210</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
@@ -2238,7 +2238,7 @@
         <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
         <v>7.4</v>
@@ -2247,34 +2247,34 @@
         <v>7.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="AV7" t="n">
         <v>6.4</v>
       </c>
       <c r="AW7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA7" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7</v>
-      </c>
       <c r="BB7" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="BD7" t="n">
         <v>6.2</v>
@@ -2283,7 +2283,7 @@
         <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
@@ -2298,19 +2298,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN7" t="n">
         <v>5</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP7" t="n">
         <v>8.4</v>
@@ -2322,13 +2322,13 @@
         <v>16.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT7" t="n">
         <v>12.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,7 +2340,7 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>7.8</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -2420,16 +2420,16 @@
         <v>2.62</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="T8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="W8" t="n">
         <v>1.18</v>
@@ -2495,22 +2495,22 @@
         <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
@@ -2519,10 +2519,10 @@
         <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
         <v>9.6</v>
@@ -2537,7 +2537,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
         <v>2.92</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -2635,64 +2635,64 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.65</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.68</v>
       </c>
       <c r="H9" t="n">
         <v>4.9</v>
       </c>
       <c r="I9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J9" t="n">
         <v>5.1</v>
       </c>
-      <c r="J9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
         <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S9" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="T9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V9" t="n">
         <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X9" t="n">
         <v>50</v>
       </c>
       <c r="Y9" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="Z9" t="n">
         <v>60</v>
@@ -2701,19 +2701,19 @@
         <v>120</v>
       </c>
       <c r="AB9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
         <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2734,16 +2734,16 @@
         <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AO9" t="n">
         <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AQ9" t="n">
         <v>38</v>
@@ -2752,7 +2752,7 @@
         <v>50</v>
       </c>
       <c r="AS9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AT9" t="n">
         <v>19</v>
@@ -2767,7 +2767,7 @@
         <v>40</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
@@ -2779,7 +2779,7 @@
         <v>34</v>
       </c>
       <c r="BB9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC9" t="n">
         <v>13.5</v>
@@ -2791,7 +2791,7 @@
         <v>38</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
         <v>21</v>
@@ -2800,65 +2800,65 @@
         <v>6.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>55</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV9" t="n">
         <v>30</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="I10" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.29</v>
@@ -2913,49 +2913,49 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V10" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y10" t="n">
         <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC10" t="n">
         <v>11</v>
@@ -2967,37 +2967,37 @@
         <v>16</v>
       </c>
       <c r="AF10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AG10" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="n">
         <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
         <v>40</v>
       </c>
       <c r="AO10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ10" t="n">
         <v>11</v>
@@ -3006,22 +3006,22 @@
         <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
         <v>14</v>
       </c>
       <c r="AX10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
@@ -3033,10 +3033,10 @@
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="BD10" t="n">
         <v>42</v>
@@ -3045,74 +3045,74 @@
         <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
         <v>4.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO10" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR10" t="n">
         <v>38</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BX10" t="n">
         <v>21</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA10" t="n">
         <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>2.04</v>
       </c>
       <c r="H11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I11" t="n">
         <v>4.5</v>
       </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.45</v>
@@ -3167,58 +3167,58 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
         <v>11.5</v>
@@ -3227,106 +3227,106 @@
         <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
         <v>23</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AS11" t="n">
-        <v>85</v>
+        <v>14.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD11" t="n">
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BF11" t="n">
         <v>17.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.5</v>
+        <v>46</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BN11" t="n">
         <v>4.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP11" t="n">
         <v>14</v>
@@ -3350,13 +3350,13 @@
         <v>38</v>
       </c>
       <c r="BW11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>28</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="H12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J12" t="n">
         <v>2.98</v>
@@ -3418,7 +3418,7 @@
         <v>1.58</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
         <v>2.72</v>
@@ -3427,7 +3427,7 @@
         <v>1.54</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q12" t="n">
         <v>2.78</v>
@@ -3442,19 +3442,19 @@
         <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y12" t="n">
         <v>9.4</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9.6</v>
       </c>
       <c r="Z12" t="n">
         <v>17.5</v>
@@ -3463,10 +3463,10 @@
         <v>120</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD12" t="n">
         <v>14.5</v>
@@ -3475,7 +3475,7 @@
         <v>48</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AG12" t="n">
         <v>15.5</v>
@@ -3502,49 +3502,49 @@
         <v>140</v>
       </c>
       <c r="AO12" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
         <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
         <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BD12" t="n">
         <v>34</v>
@@ -3559,10 +3559,10 @@
         <v>34</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BN12" t="n">
         <v>5.9</v>
@@ -3586,16 +3586,16 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU12" t="n">
         <v>4.8</v>
@@ -3604,23 +3604,23 @@
         <v>32</v>
       </c>
       <c r="BW12" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX12" t="n">
         <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
@@ -3669,58 +3669,58 @@
         <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
         <v>11.5</v>
@@ -3735,16 +3735,16 @@
         <v>19</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK13" t="n">
         <v>500</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>70</v>
       </c>
       <c r="AL13" t="n">
         <v>190</v>
@@ -3753,128 +3753,128 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AO13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF13" t="n">
         <v>7.8</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BG13" t="n">
         <v>17</v>
       </c>
-      <c r="AX13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN13" t="n">
         <v>8</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP13" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BT13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BZ13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
         <v>2.82</v>
       </c>
       <c r="H14" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K14" t="n">
         <v>2.96</v>
@@ -3926,40 +3926,40 @@
         <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N14" t="n">
         <v>2.64</v>
       </c>
       <c r="O14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P14" t="n">
         <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S14" t="n">
         <v>5.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
         <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y14" t="n">
         <v>9.800000000000001</v>
@@ -3995,10 +3995,10 @@
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="AL14" t="n">
         <v>500</v>
@@ -4010,10 +4010,10 @@
         <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.199999999999999</v>
@@ -4034,10 +4034,10 @@
         <v>13.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
@@ -4046,16 +4046,16 @@
         <v>19.5</v>
       </c>
       <c r="BA14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD14" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>28</v>
       </c>
       <c r="BE14" t="n">
         <v>10</v>
@@ -4070,13 +4070,13 @@
         <v>2.72</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ14" t="n">
         <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4109,7 +4109,7 @@
         <v>5.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW14" t="n">
         <v>8.800000000000001</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G15" t="n">
         <v>1.21</v>
@@ -4168,7 +4168,7 @@
         <v>13</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J15" t="n">
         <v>7.4</v>
@@ -4180,7 +4180,7 @@
         <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
         <v>4.5</v>
@@ -4189,7 +4189,7 @@
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
         <v>1.58</v>
@@ -4213,7 +4213,7 @@
         <v>5.7</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y15" t="n">
         <v>75</v>
@@ -4240,7 +4240,7 @@
         <v>7.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
         <v>60</v>
@@ -4270,119 +4270,119 @@
         <v>6.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AT15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU15" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB15" t="n">
         <v>6</v>
       </c>
-      <c r="AV15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BC15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>3.15</v>
       </c>
       <c r="BG15" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -4413,169 +4413,169 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
         <v>1.63</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN16" t="n">
         <v>13</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.56</v>
+        <v>4.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.51</v>
+        <v>4.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.58</v>
+        <v>4.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.62</v>
+        <v>5.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.68</v>
+        <v>6.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.58</v>
+        <v>5.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI16" t="n">
         <v>2.54</v>
@@ -4584,25 +4584,25 @@
         <v>13.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BP16" t="n">
         <v>11</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4611,7 +4611,7 @@
         <v>2.32</v>
       </c>
       <c r="BT16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU16" t="n">
         <v>6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4670,16 @@
         <v>1.94</v>
       </c>
       <c r="G17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
         <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
         <v>3.45</v>
@@ -4691,22 +4691,22 @@
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T17" t="n">
         <v>2.18</v>
@@ -4718,10 +4718,10 @@
         <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y17" t="n">
         <v>14.5</v>
@@ -4730,16 +4730,16 @@
         <v>36</v>
       </c>
       <c r="AA17" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC17" t="n">
         <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>95</v>
@@ -4781,58 +4781,58 @@
         <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AS17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
         <v>19.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BB17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC17" t="n">
         <v>19.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>46</v>
       </c>
       <c r="BE17" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG17" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ17" t="n">
         <v>12</v>
@@ -4883,14 +4883,14 @@
         <v>10.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -4927,16 +4927,16 @@
         <v>2.14</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
         <v>1.54</v>
@@ -4945,7 +4945,7 @@
         <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
         <v>1.49</v>
@@ -5005,7 +5005,7 @@
         <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
         <v>110</v>
@@ -5071,7 +5071,7 @@
         <v>20</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE18" t="n">
         <v>4.7</v>
@@ -5089,10 +5089,10 @@
         <v>2.32</v>
       </c>
       <c r="BJ18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5101,10 +5101,10 @@
         <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP18" t="n">
         <v>17.5</v>
@@ -5125,7 +5125,7 @@
         <v>5.7</v>
       </c>
       <c r="BV18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW18" t="n">
         <v>9</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,133 +857,133 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="X2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>16</v>
       </c>
-      <c r="Y2" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AS2" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
         <v>75</v>
@@ -992,95 +992,95 @@
         <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>310</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS2" t="n">
         <v>34</v>
       </c>
-      <c r="BE2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>160</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BT2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BV2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY2" t="n">
         <v>65</v>
       </c>
-      <c r="BW2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>9</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>1.26</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J3" t="n">
         <v>7.4</v>
@@ -1141,22 +1141,22 @@
         <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R3" t="n">
         <v>1.82</v>
       </c>
       <c r="S3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
@@ -1171,19 +1171,19 @@
         <v>55</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA3" t="n">
-        <v>560</v>
+        <v>680</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
         <v>17</v>
       </c>
       <c r="AD3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE3" t="n">
         <v>200</v>
@@ -1192,58 +1192,58 @@
         <v>8.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
         <v>9.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP3" t="n">
         <v>32</v>
       </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>30</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR3" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV3" t="n">
         <v>42</v>
       </c>
       <c r="AW3" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB3" t="n">
         <v>8.800000000000001</v>
@@ -1264,77 +1264,77 @@
         <v>29</v>
       </c>
       <c r="BE3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BF3" t="n">
         <v>3.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="BH3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>13</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
         <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP3" t="n">
         <v>6.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR3" t="n">
         <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
         <v>16.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX3" t="n">
         <v>85</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>8.4</v>
       </c>
       <c r="CA3" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
         <v>2.42</v>
@@ -1383,40 +1383,40 @@
         <v>3.25</v>
       </c>
       <c r="L4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.62</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.58</v>
-      </c>
       <c r="P4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
         <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1485,10 +1485,10 @@
         <v>1.42</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.45</v>
+        <v>1.31</v>
       </c>
       <c r="AV4" t="n">
         <v>1.41</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -1619,127 +1619,127 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="I5" t="n">
         <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.92</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
         <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ5" t="n">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="AK5" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT5" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
         <v>5.8</v>
@@ -1751,46 +1751,46 @@
         <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
         <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT5" t="n">
         <v>5.8</v>
@@ -1823,26 +1823,26 @@
         <v>4.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>9</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -1873,88 +1873,88 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
         <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="X6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>260</v>
       </c>
       <c r="AF6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
         <v>30</v>
@@ -1963,140 +1963,140 @@
         <v>540</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF6" t="n">
         <v>20</v>
       </c>
-      <c r="BA6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD6" t="n">
+      <c r="BG6" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF6" t="n">
+      <c r="BH6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP6" t="n">
         <v>19.5</v>
       </c>
-      <c r="BG6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BQ6" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BR6" t="n">
         <v>48</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="CA6" t="n">
         <v>7</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>50</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="K7" t="n">
         <v>6.8</v>
@@ -2157,28 +2157,28 @@
         <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="X7" t="n">
         <v>60</v>
@@ -2187,10 +2187,10 @@
         <v>150</v>
       </c>
       <c r="Z7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA7" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AB7" t="n">
         <v>19</v>
@@ -2205,10 +2205,10 @@
         <v>210</v>
       </c>
       <c r="AF7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>21</v>
@@ -2217,46 +2217,46 @@
         <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
         <v>28</v>
       </c>
       <c r="AM7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS7" t="n">
         <v>7</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.8</v>
       </c>
       <c r="AT7" t="n">
         <v>15.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX7" t="n">
         <v>12</v>
@@ -2265,25 +2265,25 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
@@ -2298,13 +2298,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
         <v>5</v>
@@ -2322,13 +2322,13 @@
         <v>16.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT7" t="n">
         <v>12.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,7 +2340,7 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>7.8</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>5.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
         <v>1.46</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J8" t="n">
         <v>5.7</v>
       </c>
       <c r="K8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.14</v>
@@ -2423,19 +2423,19 @@
         <v>1.59</v>
       </c>
       <c r="T8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="U8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V8" t="n">
         <v>2.94</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Y8" t="n">
         <v>48</v>
@@ -2444,7 +2444,7 @@
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB8" t="n">
         <v>150</v>
@@ -2462,7 +2462,7 @@
         <v>200</v>
       </c>
       <c r="AG8" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AH8" t="n">
         <v>18.5</v>
@@ -2489,58 +2489,58 @@
         <v>3.35</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD8" t="n">
         <v>7.6</v>
       </c>
-      <c r="AR8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="G9" t="n">
         <v>1.65</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>5.3</v>
@@ -2659,115 +2659,115 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="T9" t="n">
         <v>1.4</v>
       </c>
       <c r="U9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
         <v>2.52</v>
       </c>
       <c r="X9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA9" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB9" t="n">
         <v>23</v>
       </c>
       <c r="AC9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>46</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
         <v>14.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
         <v>42</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO9" t="n">
         <v>24</v>
       </c>
       <c r="AP9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>42</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>38</v>
       </c>
       <c r="AR9" t="n">
         <v>50</v>
       </c>
       <c r="AS9" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW9" t="n">
         <v>40</v>
       </c>
       <c r="AX9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
@@ -2782,7 +2782,7 @@
         <v>18.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
         <v>18.5</v>
@@ -2791,28 +2791,28 @@
         <v>38</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>55</v>
       </c>
       <c r="BM9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
         <v>5.4</v>
@@ -2824,41 +2824,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BR9" t="n">
         <v>16</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -2889,43 +2889,43 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.69</v>
       </c>
-      <c r="I10" t="n">
-        <v>1.72</v>
-      </c>
       <c r="J10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K10" t="n">
         <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S10" t="n">
         <v>2.4</v>
@@ -2937,13 +2937,13 @@
         <v>2.42</v>
       </c>
       <c r="V10" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y10" t="n">
         <v>13</v>
@@ -2952,10 +2952,10 @@
         <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC10" t="n">
         <v>11</v>
@@ -2964,7 +2964,7 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF10" t="n">
         <v>46</v>
@@ -2982,34 +2982,34 @@
         <v>130</v>
       </c>
       <c r="AK10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AO10" t="n">
         <v>6.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ10" t="n">
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU10" t="n">
         <v>9.6</v>
@@ -3018,73 +3018,73 @@
         <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BC10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BD10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF10" t="n">
         <v>28</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="n">
         <v>4.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
         <v>4.7</v>
@@ -3096,23 +3096,23 @@
         <v>10.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>21</v>
       </c>
       <c r="BY10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.45</v>
@@ -3167,46 +3167,46 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.94</v>
-      </c>
       <c r="X11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
         <v>8.199999999999999</v>
@@ -3215,103 +3215,103 @@
         <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR11" t="n">
         <v>24</v>
       </c>
-      <c r="AL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>26</v>
-      </c>
       <c r="AS11" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC11" t="n">
         <v>23</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>19.5</v>
       </c>
       <c r="BD11" t="n">
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BG11" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK11" t="n">
         <v>8.4</v>
@@ -3320,53 +3320,53 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BR11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>30</v>
       </c>
-      <c r="BS11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>28</v>
-      </c>
       <c r="CA11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
         <v>3.15</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="I12" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -3418,7 +3418,7 @@
         <v>1.58</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
         <v>2.72</v>
@@ -3436,61 +3436,61 @@
         <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
         <v>18.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI12" t="n">
         <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AL12" t="n">
         <v>160</v>
@@ -3499,16 +3499,16 @@
         <v>570</v>
       </c>
       <c r="AN12" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AO12" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -3520,64 +3520,64 @@
         <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AX12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY12" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
         <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BC12" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BD12" t="n">
         <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BG12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BH12" t="n">
         <v>2.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO12" t="n">
         <v>5.2</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT12" t="n">
         <v>5.5</v>
@@ -3601,26 +3601,26 @@
         <v>4.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -3657,172 +3657,172 @@
         <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="V13" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="W13" t="n">
         <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z13" t="n">
         <v>12.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AF13" t="n">
         <v>34</v>
       </c>
       <c r="AG13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
         <v>900</v>
       </c>
       <c r="AK13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL13" t="n">
         <v>500</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>190</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
         <v>10</v>
       </c>
       <c r="AS13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG13" t="n">
         <v>21</v>
       </c>
-      <c r="AT13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>17</v>
-      </c>
       <c r="BH13" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3831,22 +3831,22 @@
         <v>10</v>
       </c>
       <c r="BN13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP13" t="n">
         <v>46</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>4.8</v>
@@ -3855,26 +3855,26 @@
         <v>3.55</v>
       </c>
       <c r="BV13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="L14" t="n">
         <v>1.61</v>
@@ -3929,16 +3929,16 @@
         <v>1.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
         <v>1.55</v>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R14" t="n">
         <v>1.19</v>
@@ -3950,25 +3950,25 @@
         <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X14" t="n">
         <v>8.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB14" t="n">
         <v>8</v>
@@ -3980,7 +3980,7 @@
         <v>16.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AF14" t="n">
         <v>16.5</v>
@@ -3989,40 +3989,40 @@
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
         <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AT14" t="n">
         <v>6.6</v>
@@ -4034,55 +4034,55 @@
         <v>13.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AX14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="BJ14" t="n">
         <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN14" t="n">
         <v>5.5</v>
@@ -4100,7 +4100,7 @@
         <v>50</v>
       </c>
       <c r="BS14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT14" t="n">
         <v>6.4</v>
@@ -4109,26 +4109,26 @@
         <v>5.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I15" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
         <v>7.4</v>
@@ -4177,46 +4177,46 @@
         <v>9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
         <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
         <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="U15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="X15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z15" t="n">
         <v>330</v>
@@ -4225,10 +4225,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AD15" t="n">
         <v>110</v>
@@ -4237,91 +4237,91 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AI15" t="n">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="AJ15" t="n">
         <v>8.4</v>
       </c>
       <c r="AK15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="n">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR15" t="n">
-        <v>9</v>
-      </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX15" t="n">
         <v>4.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI15" t="n">
         <v>3.2</v>
@@ -4330,7 +4330,7 @@
         <v>17</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4339,10 +4339,10 @@
         <v>2.66</v>
       </c>
       <c r="BN15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BP15" t="n">
         <v>6.4</v>
@@ -4354,13 +4354,13 @@
         <v>29</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.8</v>
+        <v>2.46</v>
       </c>
       <c r="BT15" t="n">
         <v>23</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4375,14 +4375,14 @@
         <v>2.64</v>
       </c>
       <c r="BZ15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CA15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -4416,61 +4416,61 @@
         <v>1.51</v>
       </c>
       <c r="G16" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I16" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
         <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
         <v>90</v>
@@ -4485,7 +4485,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AE16" t="n">
         <v>220</v>
@@ -4503,115 +4503,115 @@
         <v>210</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO16" t="n">
         <v>420</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC16" t="n">
         <v>6.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BJ16" t="n">
         <v>13.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BP16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BT16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU16" t="n">
         <v>6</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
         <v>1.55</v>
@@ -4697,34 +4697,34 @@
         <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q17" t="n">
         <v>2.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T17" t="n">
         <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
         <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>9.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
         <v>36</v>
@@ -4736,13 +4736,13 @@
         <v>6.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
         <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF17" t="n">
         <v>10.5</v>
@@ -4754,10 +4754,10 @@
         <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK17" t="n">
         <v>25</v>
@@ -4766,10 +4766,10 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>150</v>
@@ -4781,116 +4781,116 @@
         <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
         <v>6</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>9</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB17" t="n">
         <v>20</v>
       </c>
-      <c r="BA17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>16</v>
-      </c>
       <c r="BC17" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>46</v>
       </c>
       <c r="BE17" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BF17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BH17" t="n">
         <v>2.88</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="BJ17" t="n">
         <v>12</v>
       </c>
       <c r="BK17" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN17" t="n">
         <v>4.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
         <v>9.4</v>
       </c>
-      <c r="BT17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>10</v>
-      </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H18" t="n">
         <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.54</v>
@@ -4951,28 +4951,28 @@
         <v>1.49</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
         <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
         <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X18" t="n">
         <v>11.5</v>
@@ -4981,7 +4981,7 @@
         <v>14.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA18" t="n">
         <v>130</v>
@@ -4990,7 +4990,7 @@
         <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
         <v>22</v>
@@ -4999,7 +4999,7 @@
         <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
@@ -5011,76 +5011,76 @@
         <v>110</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
         <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO18" t="n">
         <v>120</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV18" t="n">
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX18" t="n">
         <v>9</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
         <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC18" t="n">
         <v>20</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH18" t="n">
         <v>2.92</v>
@@ -5101,13 +5101,13 @@
         <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP18" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ18" t="n">
         <v>6.8</v>
@@ -5119,16 +5119,16 @@
         <v>8.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18" t="n">
         <v>65</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
         <v>1.26</v>
@@ -869,127 +869,127 @@
         <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="R2" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="S2" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="X2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Z2" t="n">
         <v>140</v>
       </c>
       <c r="AA2" t="n">
-        <v>680</v>
+        <v>540</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AD2" t="n">
         <v>48</v>
       </c>
       <c r="AE2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AK2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AQ2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AR2" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AS2" t="n">
         <v>110</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>40</v>
       </c>
       <c r="AW2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -998,40 +998,40 @@
         <v>26</v>
       </c>
       <c r="BA2" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>120</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>11.5</v>
       </c>
-      <c r="BD2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>95</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BK2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BL2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM2" t="n">
         <v>110</v>
@@ -1040,47 +1040,47 @@
         <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BV2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I3" t="n">
         <v>2.68</v>
       </c>
-      <c r="I3" t="n">
-        <v>3.05</v>
-      </c>
       <c r="J3" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M3" t="n">
         <v>1.13</v>
@@ -1138,19 +1138,19 @@
         <v>2.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q3" t="n">
         <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="T3" t="n">
         <v>1.92</v>
@@ -1159,10 +1159,10 @@
         <v>1.35</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AT3" t="n">
         <v>4.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.19</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BF3" t="n">
         <v>1.55</v>
@@ -1282,59 +1282,59 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
         <v>3.5</v>
       </c>
       <c r="H4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N4" t="n">
         <v>2.68</v>
       </c>
-      <c r="I4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z4" t="n">
         <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
         <v>200</v>
       </c>
       <c r="AK4" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
         <v>2.24</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
@@ -1721,7 +1721,7 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
         <v>200</v>
@@ -1736,13 +1736,13 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
@@ -1760,7 +1760,7 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
         <v>22</v>
@@ -1769,10 +1769,10 @@
         <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>28</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
@@ -1784,7 +1784,7 @@
         <v>2.82</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ5" t="n">
         <v>13.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H6" t="n">
         <v>6.6</v>
       </c>
       <c r="I6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>5.6</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.19</v>
@@ -1903,94 +1903,94 @@
         <v>1.1</v>
       </c>
       <c r="P6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R6" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="T6" t="n">
         <v>1.51</v>
       </c>
       <c r="U6" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Y6" t="n">
         <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AA6" t="n">
         <v>200</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD6" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AE6" t="n">
         <v>210</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>150</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK6" t="n">
         <v>16.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM6" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
         <v>3.95</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>15.5</v>
@@ -1999,37 +1999,37 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
         <v>10.5</v>
@@ -2038,13 +2038,13 @@
         <v>6.4</v>
       </c>
       <c r="BI6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK6" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>4.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2059,34 +2059,34 @@
         <v>3.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BT6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>8.199999999999999</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J7" t="n">
         <v>5.7</v>
@@ -2163,22 +2163,22 @@
         <v>1.18</v>
       </c>
       <c r="R7" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
         <v>1.32</v>
       </c>
       <c r="U7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="V7" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB7" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="AC7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AD7" t="n">
         <v>15</v>
@@ -2208,10 +2208,10 @@
         <v>200</v>
       </c>
       <c r="AG7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
         <v>19.5</v>
@@ -2226,31 +2226,31 @@
         <v>100</v>
       </c>
       <c r="AM7" t="n">
-        <v>36</v>
+        <v>790</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AP7" t="n">
         <v>60</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AV7" t="n">
         <v>12</v>
@@ -2259,10 +2259,10 @@
         <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AZ7" t="n">
         <v>14.5</v>
@@ -2271,34 +2271,34 @@
         <v>16</v>
       </c>
       <c r="BB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>9</v>
       </c>
-      <c r="BC7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,47 +2310,47 @@
         <v>12</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU7" t="n">
         <v>5.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BW7" t="n">
         <v>5.3</v>
       </c>
       <c r="BX7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -2381,151 +2381,151 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.2</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W8" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y8" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF8" t="n">
         <v>18.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
         <v>20</v>
       </c>
       <c r="AK8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AO8" t="n">
         <v>23</v>
       </c>
       <c r="AP8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AQ8" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AR8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AS8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
       </c>
       <c r="AU8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AX8" t="n">
         <v>16</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
@@ -2537,25 +2537,25 @@
         <v>38</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BG8" t="n">
         <v>21</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ8" t="n">
         <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BM8" t="n">
         <v>44</v>
@@ -2567,22 +2567,22 @@
         <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BV8" t="n">
         <v>32</v>
@@ -2594,17 +2594,17 @@
         <v>28</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -2635,31 +2635,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="I9" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.16</v>
@@ -2668,13 +2668,13 @@
         <v>2.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="S9" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T9" t="n">
         <v>1.57</v>
@@ -2683,28 +2683,28 @@
         <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
@@ -2713,10 +2713,10 @@
         <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
         <v>17.5</v>
@@ -2728,7 +2728,7 @@
         <v>130</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
@@ -2737,10 +2737,10 @@
         <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO9" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AP9" t="n">
         <v>26</v>
@@ -2752,10 +2752,10 @@
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AU9" t="n">
         <v>10.5</v>
@@ -2767,46 +2767,46 @@
         <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
         <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BC9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BD9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2815,50 +2815,50 @@
         <v>55</v>
       </c>
       <c r="BN9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP9" t="n">
         <v>36</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT9" t="n">
         <v>4.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW9" t="n">
         <v>5.9</v>
       </c>
       <c r="BX9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H10" t="n">
         <v>3.95</v>
@@ -2901,70 +2901,70 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.4</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="X10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
         <v>12.5</v>
@@ -2973,13 +2973,13 @@
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
         <v>27</v>
@@ -2991,76 +2991,76 @@
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO10" t="n">
         <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>23</v>
       </c>
       <c r="AS10" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BB10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE10" t="n">
         <v>80</v>
       </c>
       <c r="BF10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,7 +3069,7 @@
         <v>100</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO10" t="n">
         <v>4.3</v>
@@ -3078,13 +3078,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
         <v>7</v>
@@ -3096,23 +3096,23 @@
         <v>34</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY10" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
         <v>3.2</v>
@@ -3167,58 +3167,58 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
         <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
         <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
         <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
         <v>18</v>
@@ -3227,13 +3227,13 @@
         <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
         <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AK11" t="n">
         <v>110</v>
@@ -3245,16 +3245,16 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR11" t="n">
         <v>14</v>
@@ -3263,16 +3263,16 @@
         <v>34</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
         <v>15</v>
@@ -3284,10 +3284,10 @@
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BB11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC11" t="n">
         <v>29</v>
@@ -3299,22 +3299,22 @@
         <v>140</v>
       </c>
       <c r="BF11" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BG11" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3326,28 +3326,28 @@
         <v>5.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU11" t="n">
         <v>4.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
         <v>10</v>
@@ -3356,17 +3356,17 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="I12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
         <v>3.45</v>
@@ -3427,28 +3427,28 @@
         <v>1.48</v>
       </c>
       <c r="P12" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q12" t="n">
         <v>2.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V12" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="W12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -3457,7 +3457,7 @@
         <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA12" t="n">
         <v>32</v>
@@ -3475,25 +3475,25 @@
         <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3505,28 +3505,28 @@
         <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AX12" t="n">
         <v>21</v>
@@ -3538,28 +3538,28 @@
         <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
         <v>130</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
         <v>18.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI12" t="n">
         <v>2.34</v>
@@ -3568,7 +3568,7 @@
         <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,22 +3577,22 @@
         <v>160</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12" t="n">
         <v>5</v>
@@ -3604,23 +3604,23 @@
         <v>19</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX12" t="n">
         <v>40</v>
       </c>
       <c r="BY12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>42</v>
       </c>
       <c r="CA12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -3651,70 +3651,70 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
         <v>2.86</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L13" t="n">
         <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T13" t="n">
         <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13" t="n">
         <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
         <v>7.8</v>
@@ -3723,10 +3723,10 @@
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
         <v>15.5</v>
@@ -3738,13 +3738,13 @@
         <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK13" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
         <v>70</v>
@@ -3756,34 +3756,34 @@
         <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
         <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
@@ -3822,19 +3822,19 @@
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN13" t="n">
         <v>5.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP13" t="n">
         <v>23</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -3911,13 +3911,13 @@
         <v>1.22</v>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
         <v>8.800000000000001</v>
@@ -3947,16 +3947,16 @@
         <v>2.48</v>
       </c>
       <c r="T14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V14" t="n">
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="X14" t="n">
         <v>26</v>
@@ -4025,13 +4025,13 @@
         <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU14" t="n">
         <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
         <v>9</v>
@@ -4043,7 +4043,7 @@
         <v>5.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
         <v>8.800000000000001</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
         <v>1.47</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
         <v>3.05</v>
@@ -4189,43 +4189,43 @@
         <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
         <v>2.26</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V15" t="n">
         <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Z15" t="n">
         <v>85</v>
       </c>
       <c r="AA15" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
         <v>950</v>
       </c>
       <c r="AE15" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AF15" t="n">
         <v>8.199999999999999</v>
@@ -4243,40 +4243,40 @@
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ15" t="n">
         <v>14.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
         <v>290</v>
       </c>
       <c r="AN15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="AP15" t="n">
         <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>5.4</v>
@@ -4285,22 +4285,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -4309,16 +4309,16 @@
         <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="n">
         <v>3.2</v>
@@ -4330,7 +4330,7 @@
         <v>13.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4348,7 +4348,7 @@
         <v>11</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4375,14 +4375,14 @@
         <v>10</v>
       </c>
       <c r="BZ15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA15" t="n">
         <v>7.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="G16" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
         <v>1.56</v>
@@ -4437,16 +4437,16 @@
         <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
         <v>1.22</v>
@@ -4455,7 +4455,7 @@
         <v>5.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
         <v>1.79</v>
@@ -4464,10 +4464,10 @@
         <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y16" t="n">
         <v>13.5</v>
@@ -4488,7 +4488,7 @@
         <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AF16" t="n">
         <v>10.5</v>
@@ -4500,22 +4500,22 @@
         <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
         <v>140</v>
@@ -4524,25 +4524,25 @@
         <v>8.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AT16" t="n">
         <v>6.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
         <v>19</v>
       </c>
       <c r="AW16" t="n">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -4554,28 +4554,28 @@
         <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>18.5</v>
+        <v>65</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
         <v>23</v>
       </c>
       <c r="BD16" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BE16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI16" t="n">
         <v>2.62</v>
@@ -4584,13 +4584,13 @@
         <v>12</v>
       </c>
       <c r="BK16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>16</v>
+        <v>2.38</v>
       </c>
       <c r="BN16" t="n">
         <v>4.3</v>
@@ -4602,16 +4602,16 @@
         <v>15.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU16" t="n">
         <v>5.8</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>13</v>
+        <v>2.3</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>12</v>
+        <v>2.28</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G17" t="n">
         <v>2.18</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
         <v>1.54</v>
@@ -4700,22 +4700,22 @@
         <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
         <v>5.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
         <v>1.84</v>
@@ -4727,10 +4727,10 @@
         <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
         <v>7.6</v>
@@ -4739,22 +4739,22 @@
         <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -4775,19 +4775,19 @@
         <v>120</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>10.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.1</v>
+        <v>75</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
@@ -4796,19 +4796,19 @@
         <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>46</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.1</v>
+        <v>55</v>
       </c>
       <c r="BB17" t="n">
         <v>19.5</v>
@@ -4817,80 +4817,80 @@
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.9</v>
+        <v>65</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP17" t="n">
         <v>18</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR17" t="n">
         <v>40</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BT17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV17" t="n">
         <v>42</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>42</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-13.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="G2" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W2" t="n">
         <v>8</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="X2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>18.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AE2" t="n">
-        <v>180</v>
+        <v>460</v>
       </c>
       <c r="AF2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG2" t="n">
         <v>10</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK2" t="n">
         <v>12</v>
       </c>
-      <c r="AH2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
         <v>10</v>
       </c>
-      <c r="AK2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AW2" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
       </c>
       <c r="BD2" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
+        <v>200</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>250</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>910</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>85</v>
       </c>
-      <c r="BF2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>120</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>110</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>7.4</v>
-      </c>
       <c r="CA2" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1111,67 +1111,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I3" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N3" t="n">
         <v>2.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="P3" t="n">
         <v>1.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="T3" t="n">
         <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
@@ -1183,7 +1183,7 @@
         <v>42</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.31</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AT3" t="n">
         <v>4.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.42</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
         <v>1.55</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1365,100 +1365,100 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="H4" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="I4" t="n">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="J4" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="K4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
         <v>1.14</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T4" t="n">
         <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
         <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
         <v>150</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AJ4" t="n">
         <v>200</v>
       </c>
       <c r="AK4" t="n">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="AL4" t="n">
         <v>500</v>
@@ -1467,128 +1467,128 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="BH4" t="n">
         <v>2.76</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW4" t="n">
         <v>7.6</v>
       </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I5" t="n">
         <v>4.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1637,109 +1637,109 @@
         <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
         <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
         <v>260</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
         <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AO5" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>70</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
@@ -1748,101 +1748,101 @@
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BV5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>60</v>
       </c>
-      <c r="BW5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>55</v>
-      </c>
       <c r="CA5" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G6" t="n">
         <v>1.43</v>
@@ -1882,7 +1882,7 @@
         <v>6.6</v>
       </c>
       <c r="I6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
         <v>5.6</v>
@@ -1891,22 +1891,22 @@
         <v>6.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
         <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R6" t="n">
         <v>2.18</v>
@@ -1915,10 +1915,10 @@
         <v>1.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V6" t="n">
         <v>1.14</v>
@@ -1927,25 +1927,25 @@
         <v>3.25</v>
       </c>
       <c r="X6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="Z6" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AA6" t="n">
         <v>200</v>
       </c>
       <c r="AB6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="n">
         <v>17</v>
       </c>
       <c r="AD6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE6" t="n">
         <v>210</v>
@@ -1954,7 +1954,7 @@
         <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
@@ -1966,49 +1966,49 @@
         <v>16.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM6" t="n">
         <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>16</v>
@@ -2020,7 +2020,7 @@
         <v>13</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
         <v>18.5</v>
@@ -2029,22 +2029,22 @@
         <v>20</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BH6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI6" t="n">
         <v>4.7</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>55</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO6" t="n">
         <v>3.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ6" t="n">
         <v>6</v>
       </c>
       <c r="BR6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT6" t="n">
         <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>7.4</v>
       </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BZ6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
         <v>1.46</v>
@@ -2139,19 +2139,19 @@
         <v>1.51</v>
       </c>
       <c r="J7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
         <v>1.05</v>
@@ -2163,37 +2163,37 @@
         <v>1.18</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="T7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="U7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="V7" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="W7" t="n">
         <v>1.19</v>
       </c>
       <c r="X7" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
         <v>23</v>
       </c>
       <c r="AB7" t="n">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
         <v>22</v>
@@ -2202,13 +2202,13 @@
         <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF7" t="n">
         <v>200</v>
       </c>
       <c r="AG7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AH7" t="n">
         <v>18.5</v>
@@ -2229,7 +2229,7 @@
         <v>790</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>3.1</v>
@@ -2238,16 +2238,16 @@
         <v>60</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
         <v>19.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
         <v>17.5</v>
@@ -2256,13 +2256,13 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
         <v>13</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>23</v>
       </c>
       <c r="AZ7" t="n">
         <v>14.5</v>
@@ -2271,34 +2271,34 @@
         <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE7" t="n">
         <v>17.5</v>
       </c>
-      <c r="BE7" t="n">
-        <v>20</v>
-      </c>
       <c r="BF7" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BH7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BI7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9</v>
-      </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,47 +2310,47 @@
         <v>12</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
         <v>26</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BX7" t="n">
         <v>13.5</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CA7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
         <v>5.2</v>
@@ -2399,97 +2399,97 @@
         <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="S8" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="T8" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="X8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Z8" t="n">
         <v>70</v>
       </c>
       <c r="AA8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD8" t="n">
         <v>24</v>
       </c>
-      <c r="AC8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
-      </c>
       <c r="AE8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL8" t="n">
         <v>18.5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AM8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AO8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AQ8" t="n">
         <v>50</v>
@@ -2498,113 +2498,113 @@
         <v>60</v>
       </c>
       <c r="AS8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BM8" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BT8" t="n">
         <v>10.5</v>
       </c>
       <c r="BU8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>6.8</v>
       </c>
-      <c r="BV8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CA8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="I9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.26</v>
@@ -2659,34 +2659,34 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="S9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
         <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2698,13 +2698,13 @@
         <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB9" t="n">
         <v>32</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
@@ -2722,10 +2722,10 @@
         <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AK9" t="n">
         <v>60</v>
@@ -2737,28 +2737,28 @@
         <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AQ9" t="n">
         <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV9" t="n">
         <v>9.4</v>
@@ -2767,7 +2767,7 @@
         <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AY9" t="n">
         <v>19.5</v>
@@ -2791,7 +2791,7 @@
         <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG9" t="n">
         <v>5.2</v>
@@ -2800,13 +2800,13 @@
         <v>4.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2821,16 +2821,16 @@
         <v>5.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT9" t="n">
         <v>4.8</v>
@@ -2842,23 +2842,23 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BY9" t="n">
         <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA9" t="n">
         <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>3.95</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
@@ -2913,16 +2913,16 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
         <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.27</v>
@@ -2931,13 +2931,13 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
         <v>1.79</v>
@@ -2949,13 +2949,13 @@
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
         <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC10" t="n">
         <v>7.2</v>
@@ -2970,7 +2970,7 @@
         <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
@@ -2979,10 +2979,10 @@
         <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
         <v>46</v>
@@ -2997,10 +2997,10 @@
         <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
         <v>23</v>
@@ -3009,34 +3009,34 @@
         <v>55</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
         <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
         <v>38</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
         <v>46</v>
       </c>
       <c r="BB10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>40</v>
@@ -3045,22 +3045,22 @@
         <v>80</v>
       </c>
       <c r="BF10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,7 +3069,7 @@
         <v>100</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO10" t="n">
         <v>4.3</v>
@@ -3078,13 +3078,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR10" t="n">
         <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT10" t="n">
         <v>7</v>
@@ -3096,23 +3096,23 @@
         <v>34</v>
       </c>
       <c r="BW10" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="BX10" t="n">
         <v>48</v>
       </c>
       <c r="BY10" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ10" t="n">
         <v>34</v>
       </c>
       <c r="CA10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>1.58</v>
@@ -3167,76 +3167,76 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
         <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R11" t="n">
         <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
         <v>1.79</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
         <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
         <v>160</v>
@@ -3245,43 +3245,43 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>120</v>
+        <v>590</v>
       </c>
       <c r="AO11" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AP11" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY11" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
         <v>36</v>
@@ -3299,13 +3299,13 @@
         <v>140</v>
       </c>
       <c r="BF11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BG11" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BI11" t="n">
         <v>2.52</v>
@@ -3314,7 +3314,7 @@
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,28 +3323,28 @@
         <v>170</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3356,17 +3356,17 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -3403,10 +3403,10 @@
         <v>4.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
@@ -3424,7 +3424,7 @@
         <v>2.88</v>
       </c>
       <c r="O12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
         <v>1.61</v>
@@ -3439,13 +3439,13 @@
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W12" t="n">
         <v>1.31</v>
@@ -3454,7 +3454,7 @@
         <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z12" t="n">
         <v>13.5</v>
@@ -3463,7 +3463,7 @@
         <v>32</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
         <v>7.8</v>
@@ -3472,13 +3472,13 @@
         <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
         <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH12" t="n">
         <v>23</v>
@@ -3487,10 +3487,10 @@
         <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="n">
         <v>100</v>
@@ -3499,22 +3499,22 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR12" t="n">
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
         <v>9.800000000000001</v>
@@ -3526,10 +3526,10 @@
         <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY12" t="n">
         <v>14.5</v>
@@ -3538,37 +3538,37 @@
         <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE12" t="n">
         <v>130</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ12" t="n">
         <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,50 +3577,50 @@
         <v>160</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR12" t="n">
         <v>60</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX12" t="n">
         <v>40</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>42</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="H13" t="n">
         <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
         <v>2.86</v>
       </c>
       <c r="K13" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="L13" t="n">
         <v>1.62</v>
@@ -3675,16 +3675,16 @@
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.55</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.52</v>
-      </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
@@ -3693,10 +3693,10 @@
         <v>5.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
@@ -3705,85 +3705,85 @@
         <v>1.6</v>
       </c>
       <c r="X13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y13" t="n">
         <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF13" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
         <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL13" t="n">
         <v>70</v>
       </c>
       <c r="AM13" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS13" t="n">
         <v>60</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
@@ -3795,7 +3795,7 @@
         <v>65</v>
       </c>
       <c r="BB13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC13" t="n">
         <v>30</v>
@@ -3807,13 +3807,13 @@
         <v>130</v>
       </c>
       <c r="BF13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BI13" t="n">
         <v>2.46</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN13" t="n">
         <v>5.2</v>
@@ -3840,41 +3840,41 @@
         <v>23</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU13" t="n">
         <v>5.7</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
         <v>10.5</v>
       </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>10</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G14" t="n">
         <v>1.22</v>
       </c>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="K14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>1.28</v>
@@ -3929,34 +3929,34 @@
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="U14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="X14" t="n">
         <v>26</v>
@@ -3974,7 +3974,7 @@
         <v>7.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="n">
         <v>110</v>
@@ -4001,76 +4001,76 @@
         <v>17</v>
       </c>
       <c r="AL14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
         <v>510</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU14" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="AV14" t="n">
         <v>9</v>
       </c>
-      <c r="AT14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU14" t="n">
+      <c r="AW14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC14" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14" t="n">
         <v>17</v>
@@ -4088,16 +4088,16 @@
         <v>3.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BP14" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS14" t="n">
         <v>7.8</v>
@@ -4118,17 +4118,17 @@
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BZ14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
         <v>1.58</v>
       </c>
       <c r="H15" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I15" t="n">
         <v>10.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>4.4</v>
@@ -4216,7 +4216,7 @@
         <v>13.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="n">
         <v>85</v>
@@ -4237,7 +4237,7 @@
         <v>230</v>
       </c>
       <c r="AF15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
@@ -4267,122 +4267,122 @@
         <v>430</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB15" t="n">
         <v>5.4</v>
       </c>
-      <c r="AU15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI15" t="n">
         <v>2.58</v>
       </c>
       <c r="BJ15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BN15" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BO15" t="n">
         <v>3.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BT15" t="n">
         <v>12</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BZ15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
         <v>5</v>
@@ -4425,28 +4425,28 @@
         <v>5.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
         <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O16" t="n">
         <v>1.52</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.22</v>
@@ -4464,10 +4464,10 @@
         <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y16" t="n">
         <v>13.5</v>
@@ -4476,10 +4476,10 @@
         <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC16" t="n">
         <v>7.4</v>
@@ -4488,7 +4488,7 @@
         <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AF16" t="n">
         <v>10.5</v>
@@ -4500,16 +4500,16 @@
         <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
         <v>210</v>
@@ -4518,19 +4518,19 @@
         <v>24</v>
       </c>
       <c r="AO16" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP16" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
         <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT16" t="n">
         <v>6.2</v>
@@ -4551,7 +4551,7 @@
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA16" t="n">
         <v>65</v>
@@ -4563,16 +4563,16 @@
         <v>23</v>
       </c>
       <c r="BD16" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BE16" t="n">
         <v>18.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH16" t="n">
         <v>2.76</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.38</v>
+        <v>17.5</v>
       </c>
       <c r="BN16" t="n">
         <v>4.3</v>
@@ -4614,7 +4614,7 @@
         <v>8.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>2.12</v>
       </c>
       <c r="G17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
         <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.54</v>
@@ -4694,13 +4694,13 @@
         <v>2.86</v>
       </c>
       <c r="O17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
         <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R17" t="n">
         <v>1.22</v>
@@ -4712,7 +4712,7 @@
         <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
         <v>1.28</v>
@@ -4721,25 +4721,25 @@
         <v>1.84</v>
       </c>
       <c r="X17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
         <v>32</v>
       </c>
       <c r="AA17" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB17" t="n">
         <v>7.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
         <v>85</v>
@@ -4751,10 +4751,10 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -4763,7 +4763,7 @@
         <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM17" t="n">
         <v>200</v>
@@ -4772,79 +4772,79 @@
         <v>27</v>
       </c>
       <c r="AO17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ17" t="n">
         <v>10.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW17" t="n">
         <v>46</v>
       </c>
       <c r="AX17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF17" t="n">
         <v>21</v>
       </c>
       <c r="BG17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BH17" t="n">
         <v>2.86</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN17" t="n">
         <v>4.8</v>
@@ -4856,41 +4856,41 @@
         <v>18</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR17" t="n">
         <v>40</v>
       </c>
       <c r="BS17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV17" t="n">
         <v>42</v>
       </c>
       <c r="BW17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>12.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>42</v>
       </c>
       <c r="CA17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
